--- a/workspaces/btc_daily_14days/rsi/rsi_7.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_7.xlsx
@@ -575,46 +575,46 @@
         <v>44</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.870198043426392</v>
+        <v>8.841358996295362</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.80701863390804</v>
+        <v>11.76880308001005</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.68878857324668</v>
+        <v>13.64425687045006</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.54805041942711</v>
+        <v>11.51084001025804</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.56196503359824</v>
+        <v>15.51169305441159</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.48584135167124</v>
+        <v>4.471439833937673</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.954241131180112</v>
+        <v>8.925602138529378</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.76517978888833</v>
+        <v>10.73061319676967</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.429453776713991</v>
+        <v>8.402456145165274</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.02385992304324</v>
+        <v>3.014326872939257</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.819324369581906</v>
+        <v>2.810461522376123</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.133261416644807</v>
+        <v>5.117136462741861</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.992302083717036</v>
+        <v>6.970405536908743</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>9.524568973811924</v>
+        <v>9.494538491666304</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.486092236631542</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.487519356533753</v>
+        <v>-6.467303805240959</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.266225062699384</v>
+        <v>-9.237367266038213</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.372755470769228</v>
+        <v>-4.359200961805612</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.912652218431951</v>
+        <v>-4.897690855794814</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.919400517438035</v>
+        <v>4.903286294252133</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.451297439256521</v>
+        <v>2.443105709840914</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.17130391712081</v>
+        <v>-5.154998172105351</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.309043539556527</v>
+        <v>4.294812110490376</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.844177720283859</v>
+        <v>5.825306360843243</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.253452403819644</v>
+        <v>3.242993674874533</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.063662161014349</v>
+        <v>8.03770114440168</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.255942488089445</v>
+        <v>5.239200293974775</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.507874646916896</v>
+        <v>5.490209487337303</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>73</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.410671268831742</v>
+        <v>6.388860127075532</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.540782843426094</v>
+        <v>7.515313761326034</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.62994980858005</v>
+        <v>12.5874217573075</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.650765754611477</v>
+        <v>8.62175568417971</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.257859901045144</v>
+        <v>1.25290345072554</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.92749126047093</v>
+        <v>2.917477439386111</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.644412853685459</v>
+        <v>-2.636034630062866</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.485410331306369</v>
+        <v>-4.470891304367619</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4296090682743525</v>
+        <v>-0.4286245953968617</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.464040776563657</v>
+        <v>1.459067304445206</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.860979749731555</v>
+        <v>-2.851574265491955</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.45345445830597</v>
+        <v>-1.448779342174326</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.623656446216565</v>
+        <v>-4.608297794397231</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.123411963644294</v>
+        <v>1.119694157917237</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>97</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.362231782882347</v>
+        <v>9.329474184107895</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.81515131071744</v>
+        <v>9.780864191668904</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.45427311258794</v>
+        <v>10.4172221758659</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.523862090815477</v>
+        <v>8.493998231532913</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.923140663510921</v>
+        <v>5.902187530969115</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.222443121000609</v>
+        <v>6.200843263554212</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.073994800606762</v>
+        <v>4.060022607608595</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.672552534638754</v>
+        <v>5.653360509892501</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.651460862451415</v>
+        <v>-2.642918784549195</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4043248577371017</v>
+        <v>-0.4031996662282822</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.6099983258728656</v>
+        <v>-0.607789466551715</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.5755346031319135</v>
+        <v>-0.5736217628528877</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9976553959105772</v>
+        <v>-0.9938802620015608</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.781318424744526</v>
+        <v>-1.775377159692169</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>98</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.608602496116546</v>
+        <v>2.597577264924674</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.038811021675713</v>
+        <v>3.026255465773048</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.707663632760259</v>
+        <v>5.685156473554343</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.754650729589436</v>
+        <v>1.746723948559243</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8268410119997895</v>
+        <v>-0.8254599478157303</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.53607004170857</v>
+        <v>2.526138864942418</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4076122336154313</v>
+        <v>0.4056364089399835</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.06032376263985384</v>
+        <v>-0.06061964562410083</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.923573549677215</v>
+        <v>1.916683235116011</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.04906978800242001</v>
+        <v>0.04868010549925827</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.156530348601251</v>
+        <v>-0.1557802068819427</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1219410091999578</v>
+        <v>-0.1215027318849167</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.550712061573698</v>
+        <v>3.538899201400376</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.754733751677719</v>
+        <v>1.748712888697845</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>124</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.106341546016424</v>
+        <v>-4.093941412430858</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.912633856286973</v>
+        <v>-4.897419823564</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.501843264316442</v>
+        <v>-4.489086204770629</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.565641165148726</v>
+        <v>-3.554958324631706</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.683639474950247</v>
+        <v>-1.679098560885684</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.846692349627098</v>
+        <v>-7.819966654541645</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.549576882068429</v>
+        <v>-9.515935692545369</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-11.63633991833107</v>
+        <v>-11.59510556277278</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.234834654100979</v>
+        <v>-5.216454494665065</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-9.32245561488174</v>
+        <v>-9.289233116069916</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-11.14807097894983</v>
+        <v>-11.10782427189243</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-10.3076046044546</v>
+        <v>-10.27058131214795</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-13.9688094407071</v>
+        <v>-13.91846566792349</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-11.29370536131926</v>
+        <v>-11.25326209484396</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>145</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.838265906416872</v>
+        <v>-2.829647581108716</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.691553285139541</v>
+        <v>-1.68720536476139</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.396760758080205</v>
+        <v>-1.394626195964385</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.32590622073208</v>
+        <v>6.30043248031231</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.098247976756632</v>
+        <v>5.077783705032182</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.127822627603237</v>
+        <v>-0.1278890217926474</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.004427122484302</v>
+        <v>5.982516810115449</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.082553824832267</v>
+        <v>2.075685339718682</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.022367201982298</v>
+        <v>2.015035724593339</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.170110083739104</v>
+        <v>1.166672674037152</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.656103371347179</v>
+        <v>1.651590831250381</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.383068260645793</v>
+        <v>2.375507290192786</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.037459133902296</v>
+        <v>4.024374946780249</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.597551656493621</v>
+        <v>3.585447582575398</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.902245133027435</v>
+        <v>2.914351342468208</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.867717967340468</v>
+        <v>-0.8691230195248778</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.282742781695916</v>
+        <v>1.290300864359168</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.132818800598464</v>
+        <v>2.143347890096479</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.920149785114312</v>
+        <v>5.943800043850736</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.940794394648265</v>
+        <v>6.966487734464401</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11.18195620607204</v>
+        <v>11.22285779656162</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>8.559979178156865</v>
+        <v>8.590399897688883</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.896162084641453</v>
+        <v>4.913986008646987</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.052720707746218</v>
+        <v>4.066643268703928</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.129515922581831</v>
+        <v>3.13941560287428</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2777147092402572</v>
+        <v>0.2777192378195608</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.746768680978228</v>
+        <v>2.755305551479836</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.780467494228887</v>
+        <v>-2.791364011627664</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.9656811766453686</v>
+        <v>0.9804102410414046</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.207195581955013</v>
+        <v>2.232714045523174</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.106100590278047</v>
+        <v>-5.146388542073666</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.05505555176136312</v>
+        <v>0.06410681437893828</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4799197254623166</v>
+        <v>-0.4761448459498183</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.440674495610651</v>
+        <v>-1.450220315069927</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.155666507650629</v>
+        <v>-2.170815287346784</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.359459951687825</v>
+        <v>-1.370722422056382</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.160518397014819</v>
+        <v>-0.1599021580656128</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.266641555125958</v>
+        <v>-2.288796416961461</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.682115796625034</v>
+        <v>0.6859082540249446</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.608623990315927</v>
+        <v>2.630903919233468</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.856837694512485</v>
+        <v>-2.886937575300799</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.987756747671753</v>
+        <v>-1.000539678570959</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>160</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.618438320209975</v>
+        <v>-5.601991810368503</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2699880668259098</v>
+        <v>0.2671142419226342</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.374880639770964</v>
+        <v>-1.372572072065964</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6195214203782484</v>
+        <v>-0.6205822882316099</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.219677018554421</v>
+        <v>3.206048314606278</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.774495194680981</v>
+        <v>9.740821930678322</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8.441494026354469</v>
+        <v>8.411907705987808</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.601923747432338</v>
+        <v>8.573028451420427</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.533953267450599</v>
+        <v>3.521491510439887</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.429274391509686</v>
+        <v>1.425098158233332</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.6558431518264527</v>
+        <v>-0.6527920821702011</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-6.263166670118181</v>
+        <v>-6.241891635271173</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-7.314999271148444</v>
+        <v>-7.289273749700889</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.437256997488674</v>
+        <v>-6.41455241742446</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>159</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.550042093795028</v>
+        <v>-1.545986327178795</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.532684889149074</v>
+        <v>-2.526079700270515</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.361754580354962</v>
+        <v>3.347758980541265</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.864412973773767</v>
+        <v>2.851052189561017</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.068319364872075</v>
+        <v>1.060692765811368</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.625827754204956</v>
+        <v>2.613393966841585</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.6067905976474322</v>
+        <v>-0.6080395718452536</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4453004776289404</v>
+        <v>-0.4457850593673385</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1235444925353235</v>
+        <v>0.1216172765255763</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.161649836334455</v>
+        <v>1.157943542616515</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9560979274928201</v>
+        <v>0.9538531511445285</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.621143630497244</v>
+        <v>1.617224131466571</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.61649731017485</v>
+        <v>5.599877193695477</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.498522327225729</v>
+        <v>6.478529343581542</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>184</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.406481798470594</v>
+        <v>-1.402442651811164</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.191968454913365</v>
+        <v>-5.17457910480821</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.869445857162134</v>
+        <v>-2.861949859950663</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.545549647004393</v>
+        <v>-6.525458683375831</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.10360332696726</v>
+        <v>-1.104091172873744</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2618097077167292</v>
+        <v>-0.2650463405385395</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.286313745431343</v>
+        <v>1.277830301285753</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.2706198220255871</v>
+        <v>-0.2718192834695827</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.8766357125610611</v>
+        <v>-0.8750723579582385</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4491533256686537</v>
+        <v>0.4476345156432728</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.937199825807738</v>
+        <v>-1.928920304978966</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.175943076488949</v>
+        <v>-5.154964788186689</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.509450146774967</v>
+        <v>-4.490360706222631</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.985865154075597</v>
+        <v>-6.958030678294172</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.06625385419078356</v>
+        <v>-0.06602875354536764</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.163264360358703</v>
+        <v>-2.165630124004153</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.587259280547521</v>
+        <v>-1.588307543356947</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.856706980501457</v>
+        <v>-4.861642733489781</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.797660899156341</v>
+        <v>-8.806851365679606</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.382174538873116</v>
+        <v>-3.384844485968983</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-6.869506323968402</v>
+        <v>-6.876476613110285</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.849569821325474</v>
+        <v>-6.857156109229372</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.830933600288091</v>
+        <v>-9.842370892792012</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-10.68172741096692</v>
+        <v>-10.69474023738875</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-8.455483286015735</v>
+        <v>-8.46629382314029</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-8.424128083499056</v>
+        <v>-8.435378706357319</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.436991303504989</v>
+        <v>-5.444761554579046</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.187543430708409</v>
+        <v>-5.195040222302652</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.988487825160242</v>
+        <v>-3.02221053636633</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.114912923273245</v>
+        <v>-3.152807516277846</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.034534105117352</v>
+        <v>-1.039252304770599</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.342790636230703</v>
+        <v>1.365141602194463</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.570119353891464</v>
+        <v>1.597169090736614</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.355790827688857</v>
+        <v>2.397424160253308</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2955098319874168</v>
+        <v>0.3073746321079867</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.315530615954586</v>
+        <v>2.34537955658574</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.234199000151506</v>
+        <v>5.294657571791959</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.389509585364117</v>
+        <v>5.445049448959992</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>5.190360431312676</v>
+        <v>5.240149600727683</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.747536025224392</v>
+        <v>2.761814252407831</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.632691508052055</v>
+        <v>0.6221584111030154</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.375791721208962</v>
+        <v>1.374392306193371</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>186</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.031072728812369</v>
+        <v>-3.022407684976294</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.642646341776263</v>
+        <v>-4.628644549087902</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.037515048372974</v>
+        <v>-5.024783910173063</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6061866469482737</v>
+        <v>-0.6062317346881017</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.6069734534184121</v>
+        <v>-0.6075513962663024</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.997703558713624</v>
+        <v>-2.992821786145612</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.007773829654845</v>
+        <v>-2.004141604413064</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.938283374422767</v>
+        <v>-1.933585598036956</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.07730498383988</v>
+        <v>-3.068667320854857</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.854301549301255</v>
+        <v>-2.844613005605837</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3672605294170026</v>
+        <v>-0.3638564558898949</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.492061155699879</v>
+        <v>-2.480578278540939</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.296156448607221</v>
+        <v>-1.287929663679265</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.123917251925114</v>
+        <v>-2.113477148607402</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>183</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.766662363925633</v>
+        <v>-2.757149010986964</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.831787889458631</v>
+        <v>-3.817627323316437</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.9479680714648069</v>
+        <v>-0.9456842696872343</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2712668514256151</v>
+        <v>-0.2723788986965161</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.356136153929356</v>
+        <v>-1.354459375717887</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.790934653372169</v>
+        <v>-3.782598030543333</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.0502239288389319</v>
+        <v>-0.05207090754153398</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.347259073452236</v>
+        <v>-4.334037161373502</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.674553216619202</v>
+        <v>-1.668669220280606</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.4335617234876</v>
+        <v>-1.4264794811778</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.640333449491628</v>
+        <v>-1.632245573620096</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.5137778677314344</v>
+        <v>-0.5063142207232048</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.03161408184274</v>
+        <v>-2.019465006531483</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.329309459195329</v>
+        <v>-2.316191761686646</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>178</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.67321360110892</v>
+        <v>-8.641112434205105</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.35220294441006</v>
+        <v>-6.326284996102459</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.376285134152845</v>
+        <v>-3.365056326670434</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-5.493223012781364</v>
+        <v>-5.476362783524948</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.893637026915329</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.22858431260972</v>
+        <v>-10.19605511639515</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-14.25378298370818</v>
+        <v>-14.20649887872844</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-12.48067844404788</v>
+        <v>-12.43632717317569</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-13.67496798970274</v>
+        <v>-13.62601216807882</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-12.84746242101543</v>
+        <v>-12.79910179772984</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-13.62474491408842</v>
+        <v>-13.57317871632429</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-9.65570681001131</v>
+        <v>-9.614805655609921</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.13146698598127</v>
+        <v>-6.102475996891897</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.881006394904261</v>
+        <v>-5.852754664615745</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>172</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.749252273698346</v>
+        <v>-0.7405909773872494</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.197313648221119</v>
+        <v>5.184351146142603</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.31407284860127</v>
+        <v>1.309670884438866</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.462650762977212</v>
+        <v>-1.457593214972611</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.58246732688665</v>
+        <v>-2.573807339126191</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.447816086845407</v>
+        <v>-3.434201926576485</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.953520599142131</v>
+        <v>-2.939323735972799</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.589063428709551</v>
+        <v>-4.565258797789973</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.237190811350644</v>
+        <v>-5.209856762161316</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.929937971515209</v>
+        <v>-4.901318425406629</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.890742445208026</v>
+        <v>-6.853608684884804</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.113778293314169</v>
+        <v>-5.081228441081564</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.118369234804021</v>
+        <v>-6.082878400863748</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.949460349932899</v>
+        <v>-2.926180324401351</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>177</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.340895947328619</v>
+        <v>-3.318697730861324</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4326955489934363</v>
+        <v>-0.4243343324437703</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.217394764064537</v>
+        <v>-4.198726378238987</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.652113382869537</v>
+        <v>-4.631821243047881</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.495619343704412</v>
+        <v>-3.480763111170326</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9382904003390351</v>
+        <v>-0.9321877649862813</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4592023773971263</v>
+        <v>-0.4523023102077772</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.061447994045515</v>
+        <v>-2.042641815324849</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.12652094679617</v>
+        <v>-2.105837361178672</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1514471825942465</v>
+        <v>-0.1364447816328394</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.77285683791834</v>
+        <v>0.785922148281081</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2357206511566403</v>
+        <v>0.2531560024869535</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.320579272681201</v>
+        <v>-1.297042111282742</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.5008426264270653</v>
+        <v>-0.4823490275940969</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>177</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.003736821032966</v>
+        <v>3.995634093583362</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.087078462305989</v>
+        <v>4.075223132069659</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.127238004296913</v>
+        <v>3.114559789262167</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.562575882667126</v>
+        <v>1.557675789772169</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.800704089467132</v>
+        <v>-1.789956965894049</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.756624853898245</v>
+        <v>0.7560252644722638</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.852212897992857</v>
+        <v>-3.826232758076543</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9314703269988058</v>
+        <v>-0.9127666409436301</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.129592251036534</v>
+        <v>-2.102766056938563</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.855027615373935</v>
+        <v>-1.827027446598805</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.067109953044849</v>
+        <v>-2.035915002000856</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.879875060207233</v>
+        <v>-4.831589760224908</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.031055205354505</v>
+        <v>-2.991957365520094</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.777639687603063</v>
+        <v>-2.742236033243806</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.262659240765629</v>
+        <v>7.34275787019196</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.602305139996574</v>
+        <v>2.621518257037046</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.378168140716987</v>
+        <v>0.38051880921887</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.320847019358375</v>
+        <v>-1.348471371990449</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.18951225337419</v>
+        <v>1.197859525197075</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.486954191089929</v>
+        <v>1.500546491950942</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.748463886000444</v>
+        <v>1.743134442466058</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.341539585239133</v>
+        <v>4.357148004106307</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.84074306068873</v>
+        <v>1.806835446972947</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.810547029262878</v>
+        <v>3.79899654321089</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.5541337932132961</v>
+        <v>0.4834328727487289</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.9800270813280889</v>
+        <v>0.8988380041012292</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.173903096468877</v>
+        <v>1.099701405578614</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.035493160257772</v>
+        <v>-1.135049311834536</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.0245472913008129</v>
+        <v>0.006869555688844287</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.2906715200631</v>
+        <v>1.292146230207187</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.262470567828416</v>
+        <v>-1.282214776253696</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.851641895652534</v>
+        <v>-1.886292887508255</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.109487571156237</v>
+        <v>-3.159045346442412</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.092621173009043</v>
+        <v>-2.127272164864763</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.858616332740347</v>
+        <v>2.868253610496872</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.110771947400238</v>
+        <v>3.109745959818937</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.477459002711193</v>
+        <v>3.465728765151155</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.914192283321192</v>
+        <v>1.877164304517287</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.444247159698428</v>
+        <v>1.385831280540835</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.6665607344540945</v>
+        <v>-0.7695665840115424</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.3652913972422667</v>
+        <v>-0.459894187657099</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.8435542774466001</v>
+        <v>-0.9400998626800785</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>124</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.345271357209377</v>
+        <v>2.34422599882663</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.540149357148344</v>
+        <v>1.539659639707658</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.951732263455035</v>
+        <v>1.949754558406582</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.143821055550426</v>
+        <v>-1.140868624442405</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.908048722235534</v>
+        <v>-4.900166154970975</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.603454084594667</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.469534050179213</v>
+        <v>-1.464975910924615</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.943413127243716</v>
+        <v>-1.936717448960714</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.416340200110092</v>
+        <v>0.4216375035666644</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3718158024580731</v>
+        <v>0.377963931442018</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.257495258974153</v>
+        <v>-2.246144231585191</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1972021284175725</v>
+        <v>0.2075937644698271</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.199456664968203</v>
+        <v>2.206693992234598</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.642406587228976</v>
+        <v>1.649963711607661</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>140</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.922009748781406</v>
+        <v>-3.913514810200887</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.390726218888524</v>
+        <v>-3.383570092106559</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.642737782627961</v>
+        <v>-6.631861417750819</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.226770364306184</v>
+        <v>-7.212890558801178</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.479477293664068</v>
+        <v>-3.470555830970703</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.467749641662685</v>
+        <v>-2.461002267155486</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.981054787506402</v>
+        <v>-3.970581250958048</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1692091570358158</v>
+        <v>-0.1625239005736034</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.9475054250997346</v>
+        <v>-0.9378095010416274</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.230975736603909</v>
+        <v>-3.216506114641028</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.430410152229314</v>
+        <v>4.435883418184289</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.746873109049751</v>
+        <v>3.755980861244012</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2498823130080083</v>
+        <v>-0.2357023211295086</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7147541484916573</v>
+        <v>-0.7002667031388867</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.028685573595382</v>
+        <v>5.050351488707292</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.647200456206299</v>
+        <v>1.643111360729328</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3673759973973176</v>
+        <v>0.3553855112755997</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.267540634429601</v>
+        <v>2.25713545916971</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9257478372796868</v>
+        <v>-0.9641224256021417</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.168128908413635</v>
+        <v>-4.229578577058533</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1719161353759873</v>
+        <v>0.1371776965699567</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6481204341440687</v>
+        <v>-0.6982381862879024</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.95986106314033</v>
+        <v>1.919333356101227</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.669318664523281</v>
+        <v>4.640636742501869</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.357989568515869</v>
+        <v>5.328740561041442</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.180632595164411</v>
+        <v>7.148838004101108</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.878245057373128</v>
+        <v>5.835726250299167</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.353820647175745</v>
+        <v>4.299733296861106</v>
       </c>
     </row>
     <row r="31">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 6.277</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4087~4100</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4087</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1275846616733887</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 9.419</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4043~4056</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4043</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.225193744273092</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 12.56</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4001~4014</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4001</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.201460243478536</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 15.7</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3928~3941</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3928</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.3239381933386269</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 18.84</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3831~3844</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3831</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.5683602765055014</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 21.99</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3733~3746</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3733</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.6514735577967343</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 25.13</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3609~3622</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3609</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.5331953605191941</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 28.27</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3464~3477</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3464</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.4370678859275472</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 31.41</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3326~3338</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3326</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.5761225622710882</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 34.55</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3169~3179</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3169</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.6532369990397981</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 37.7</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3009~3019</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3009</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.3900928415746634</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 40.84</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2850~2860</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2850</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.3256061523778015</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 43.98</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2666~2676</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2666</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.2512858538422691</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 47.12</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2461~2470</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2461</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.2667176724366911</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 50.26</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2262~2268</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2262</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.02430251774084269</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 53.41</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2076~2082</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2076</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.2443138411733159</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 56.55</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1893~1899</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1893</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.5344711058037106</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 59.69</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1715~1721</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1715</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.486805723950397</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 62.83</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1543~1549</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1543</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.735096218201903</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 65.97</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1366~1372</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1366</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.389943603988272</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 69.12</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1189~1195</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1189</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.150913144225171</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 72.26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1028~1031</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1028</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.337793493563062</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 75.4</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>891~892</t>
-        </is>
+      <c r="B28" t="n">
+        <v>891</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.54243611925191</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 78.54</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>767~768</t>
-        </is>
+      <c r="B29" t="n">
+        <v>767</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.412811679790025</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 81.68</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>627~628</t>
-        </is>
+      <c r="B30" t="n">
+        <v>627</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.602103081063909</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 84.83</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>515~515</t>
-        </is>
+      <c r="B31" t="n">
+        <v>515</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.069668475906525</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 87.97</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>385~385</t>
-        </is>
+      <c r="B32" t="n">
+        <v>385</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.311756484984826</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 91.11</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>268~268</t>
-        </is>
+      <c r="B33" t="n">
+        <v>268</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1185019782974877</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 94.25</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>165~165</t>
-        </is>
+      <c r="B34" t="n">
+        <v>165</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.2338344070627443</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 97.39</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.077990251218594</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 6.277</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5.83989501312336</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 9.419</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>128~128</t>
-        </is>
+      <c r="B7" t="n">
+        <v>128</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>6.881561679790025</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 12.56</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>170~170</t>
-        </is>
+      <c r="B8" t="n">
+        <v>170</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.565385209201786</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 15.7</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>243~243</t>
-        </is>
+      <c r="B9" t="n">
+        <v>243</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>5.119730404069863</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 18.84</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>340~340</t>
-        </is>
+      <c r="B10" t="n">
+        <v>340</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>6.330091091554735</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 21.99</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>438~438</t>
-        </is>
+      <c r="B11" t="n">
+        <v>438</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>5.497429259698706</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 25.13</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>562~562</t>
-        </is>
+      <c r="B12" t="n">
+        <v>562</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>3.378447800786461</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 28.27</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>707~707</t>
-        </is>
+      <c r="B13" t="n">
+        <v>707</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>2.103449940044619</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 31.41</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>845~846</t>
-        </is>
+      <c r="B14" t="n">
+        <v>845</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.234694067496875</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 34.55</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1002~1005</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1002</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.033924863869629</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 37.7</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1162~1165</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1162</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.982956529575425</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 40.84</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1321~1324</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1321</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.6787671178564949</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 43.98</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1505~1508</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1505</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.4243335630791449</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 47.12</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1710~1714</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1710</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.3653714814236366</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 50.26</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1909~1916</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1909</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.0117808864706106</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 53.41</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2095~2102</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2095</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.257472573302266</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 56.55</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2278~2285</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2278</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.4584273792909386</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 59.69</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2456~2463</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2456</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.052106610912375</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 62.83</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2628~2635</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2628</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.032337750950006</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 65.97</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2805~2812</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2805</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.177648846525763</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 69.12</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2982~2989</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2982</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.8708220605913723</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 72.26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3143~3153</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3143</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.4477675304858977</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 75.4</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3280~3292</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3280</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.4278247114614899</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 78.54</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3404~3416</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3404</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.3271619736057616</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 81.68</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3544~3556</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3544</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.4686914135733105</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 84.83</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3656~3669</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3656</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.2993799936904864</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 87.97</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3786~3799</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3786</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.2428460590886345</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 91.11</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3903~3916</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3903</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.01642095555215661</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 94.25</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4006~4019</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4006</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.01769808632095504</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 97.39</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4087~4100</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4087</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.03002368606362893</v>

--- a/workspaces/btc_daily_14days/rsi/rsi_7.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_7.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-7 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-7 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>44</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.841358996295362</v>
+        <v>8.853847478098544</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.76880308001005</v>
+        <v>11.78168262823554</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.64425687045006</v>
+        <v>13.65723736221596</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.51084001025804</v>
+        <v>11.52379352368286</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.51169305441159</v>
+        <v>15.52478275232695</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.471439833937673</v>
+        <v>4.484458597863949</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.925602138529378</v>
+        <v>8.93864911176955</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.73061319676967</v>
+        <v>10.74377819089984</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.402456145165274</v>
+        <v>8.415640785627197</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.014326872939257</v>
+        <v>3.027719172493839</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.810461522376123</v>
+        <v>2.823909114005104</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.117136462741861</v>
+        <v>5.130582554615685</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.970405536908743</v>
+        <v>6.983958564061417</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>9.494538491666304</v>
+        <v>9.484108855968152</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.486092236631542</v>
+        <v>-2.473613491467162</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.467303805240959</v>
+        <v>-6.454438342437079</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.237367266038213</v>
+        <v>-9.224402819578145</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.359200961805612</v>
+        <v>-4.34625773104257</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.897690855794814</v>
+        <v>-4.884612869846492</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.903286294252133</v>
+        <v>4.916304803463831</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.443105709840914</v>
+        <v>2.456149523130527</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.154998172105351</v>
+        <v>-5.141839379783192</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.294812110490376</v>
+        <v>4.307995222987913</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.825306360843243</v>
+        <v>5.838699102263135</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.242993674874533</v>
+        <v>3.256441150123877</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.03770114440168</v>
+        <v>8.051147481109105</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.239200293974775</v>
+        <v>5.252753157217271</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.490209487337303</v>
+        <v>5.479779851640231</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>73</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.388860127075532</v>
+        <v>6.401344998470883</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.515313761326034</v>
+        <v>7.528188630512091</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.5874217573075</v>
+        <v>12.60040028870238</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.62175568417971</v>
+        <v>8.634706178754037</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.25290345072554</v>
+        <v>1.265983979878214</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.917477439386111</v>
+        <v>2.930494282706384</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.636034630062866</v>
+        <v>-2.622993739282172</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.470891304367619</v>
+        <v>-4.457732951769607</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4286245953968617</v>
+        <v>-0.4154434273078778</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.459067304445206</v>
+        <v>1.472458596414249</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.851574265491955</v>
+        <v>-2.838128243236163</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.448779342174326</v>
+        <v>-1.435334378586838</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.608297794397231</v>
+        <v>-4.59474565261975</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.119694157917237</v>
+        <v>1.109264522220329</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>97</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.329474184107895</v>
+        <v>9.341960248052139</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.780864191668904</v>
+        <v>9.793739633139609</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.4172221758659</v>
+        <v>10.43019823614662</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.493998231532913</v>
+        <v>8.506947629446294</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.902187530969115</v>
+        <v>5.915269603426609</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.200843263554212</v>
+        <v>6.213860810225668</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.060022607608595</v>
+        <v>4.073065510121602</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.653360509892501</v>
+        <v>5.666521912858379</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.642918784549195</v>
+        <v>-2.629739152510403</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4031996662282822</v>
+        <v>-0.3898094765997797</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.607789466551715</v>
+        <v>-0.5943435108893524</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.5736217628528877</v>
+        <v>-0.5601770132212707</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9938802620015608</v>
+        <v>-0.9803280609326137</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.775377159692169</v>
+        <v>-1.785806795391267</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>98</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.597577264924674</v>
+        <v>2.610055643685207</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.026255465773048</v>
+        <v>3.039123763172917</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.685156473554343</v>
+        <v>5.698127629925487</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.746723948559243</v>
+        <v>1.759667290156052</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8254599478157303</v>
+        <v>-0.8123835031594595</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.526138864942418</v>
+        <v>2.539153171660843</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4056364089399835</v>
+        <v>0.4186763675391632</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.06061964562410083</v>
+        <v>-0.04746159681215545</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.916683235116011</v>
+        <v>1.929863458138669</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.04868010549925827</v>
+        <v>0.06206964055311914</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1557802068819427</v>
+        <v>-0.1423347527705019</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1215027318849167</v>
+        <v>-0.1080583150321672</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.538899201400376</v>
+        <v>3.552451522749379</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.748712888697845</v>
+        <v>1.738283252999693</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.093941412430858</v>
+        <v>-3.670047538207285</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.897419823564</v>
+        <v>-4.47945265181685</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.489086204770629</v>
+        <v>-4.077337995072106</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.554958324631706</v>
+        <v>-3.149557937461807</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.679098560885684</v>
+        <v>-1.292761251100558</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.819966654541645</v>
+        <v>-7.382091137731855</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.515935692545369</v>
+        <v>-9.065037244465906</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-11.59510556277278</v>
+        <v>-11.13108562986732</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.216454494665065</v>
+        <v>-4.803829550882902</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-9.289233116069916</v>
+        <v>-8.850509540933274</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-11.10782427189243</v>
+        <v>-10.65603420020349</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-10.27058131214795</v>
+        <v>-9.825118710073667</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-13.91846566792349</v>
+        <v>-13.44697619993989</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-11.25326209484396</v>
+        <v>-10.82498205312275</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.829647581108716</v>
+        <v>-3.16554103319352</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.68720536476139</v>
+        <v>-2.003711292050056</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.394626195964385</v>
+        <v>-1.70634689810089</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.30043248031231</v>
+        <v>6.041134817917772</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.077783705032182</v>
+        <v>4.813768836221776</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1278890217926474</v>
+        <v>-0.4302736399249412</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.982516810115449</v>
+        <v>5.723092580940929</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.075685339718682</v>
+        <v>1.792397862877607</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.015035724593339</v>
+        <v>1.731688399742623</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.166672674037152</v>
+        <v>0.883453712903524</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.651590831250381</v>
+        <v>1.373131603079798</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.375507290192786</v>
+        <v>2.101753383855055</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.024374946780249</v>
+        <v>3.765013547440276</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.297240169099467</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>138</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.914351342468208</v>
+        <v>2.552071164895487</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8691230195248778</v>
+        <v>-0.8561530285402483</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.290300864359168</v>
+        <v>0.9160536625129154</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.143347890096479</v>
+        <v>2.156283437778498</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.943800043850736</v>
+        <v>5.95687398697433</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.966487734464401</v>
+        <v>6.97949814223373</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11.22285779656162</v>
+        <v>11.23589818394107</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>8.590399897688883</v>
+        <v>8.603556768309154</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.913986008646987</v>
+        <v>4.927163101198637</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.066643268703928</v>
+        <v>4.080030303755258</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.13941560287428</v>
+        <v>3.152858915563058</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2777192378195608</v>
+        <v>0.2911617325825446</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.755305551479836</v>
+        <v>2.768856864912294</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.791364011627664</v>
+        <v>-2.801793647325646</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.9804102410414046</v>
+        <v>0.9830810572782127</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.232714045523174</v>
+        <v>1.890174752754696</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.146388542073666</v>
+        <v>-5.106434981721691</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.06410681437893828</v>
+        <v>0.07068266530788492</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4761448459498183</v>
+        <v>-0.4657294544061159</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.450220315069927</v>
+        <v>-1.430518121475934</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.170815287346784</v>
+        <v>-2.147151748349053</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.370722422056382</v>
+        <v>-1.349667239470861</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1599021580656128</v>
+        <v>-0.1471619777824884</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.288796416961461</v>
+        <v>-2.259861139698529</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6859082540249446</v>
+        <v>0.6966873644081417</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.630903919233468</v>
+        <v>2.628705853977102</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.886937575300799</v>
+        <v>-2.852257665191608</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.000539678570959</v>
+        <v>-0.7287795214771862</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>160</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.601991810368503</v>
+        <v>-5.58946952069288</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2671142419226342</v>
+        <v>0.2800240514986854</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.372572072065964</v>
+        <v>-1.359564940648362</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6205822882316099</v>
+        <v>-0.6077645523660209</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.206048314606278</v>
+        <v>3.217749628979384</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.740821930678322</v>
+        <v>9.750461176226906</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8.411907705987808</v>
+        <v>8.421982583415215</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.573028451420427</v>
+        <v>8.583291182447383</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.521491510439887</v>
+        <v>3.533417397138635</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.425098158233332</v>
+        <v>1.438062685332852</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.6527920821702011</v>
+        <v>-0.6390477402418213</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-6.241891635271173</v>
+        <v>-6.22632507115339</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-7.289273749700889</v>
+        <v>-7.273151991788566</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.41455241742446</v>
+        <v>-6.424982053122612</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>159</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.545986327178795</v>
+        <v>-1.533464037503173</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.526079700270515</v>
+        <v>-2.513169890694464</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.347758980541265</v>
+        <v>3.360766111958867</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.851052189561017</v>
+        <v>2.862638064181233</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.060692765811368</v>
+        <v>1.07298719954052</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.613393966841585</v>
+        <v>2.625147160386973</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.6080395718452536</v>
+        <v>-0.5951415589419682</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4457850593673385</v>
+        <v>-0.4326904366233677</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1216172765255763</v>
+        <v>0.1345917917231105</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.157943542616515</v>
+        <v>1.170952429575465</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9538531511445285</v>
+        <v>0.9670664461569913</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.617224131466571</v>
+        <v>1.630271529415687</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.599877193695477</v>
+        <v>5.611765107708884</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.478529343581542</v>
+        <v>6.46809970788339</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>184</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.402442651811164</v>
+        <v>-1.389920362135541</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.17457910480821</v>
+        <v>-5.161669295232159</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.861949859950663</v>
+        <v>-2.848942728533061</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.525458683375831</v>
+        <v>-6.51054746494971</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.104091172873744</v>
+        <v>-1.091092152675095</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2650463405385395</v>
+        <v>-0.2523821252036882</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.277830301285753</v>
+        <v>1.290001199833739</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.2718192834695827</v>
+        <v>-0.2588008569691667</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.8750723579582385</v>
+        <v>-0.8617534845103023</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4476345156432728</v>
+        <v>0.4608585331151502</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.928920304978966</v>
+        <v>-1.914658271899199</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.154964788186689</v>
+        <v>-5.139431141592887</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.490360706222631</v>
+        <v>-4.474903962622214</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.958030678294172</v>
+        <v>-6.968460313992324</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>205</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.06602875354536764</v>
+        <v>-0.05350646386974489</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.165630124004153</v>
+        <v>-2.152720314428102</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.588307543356947</v>
+        <v>-1.575300411939345</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.861642733489781</v>
+        <v>-4.846994658906951</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.806851365679606</v>
+        <v>-8.790644543247609</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.384844485968983</v>
+        <v>-3.63162251777981</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-6.876476613110285</v>
+        <v>-6.8611428241543</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.857156109229372</v>
+        <v>-6.841493948591086</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.842370892792012</v>
+        <v>-9.825396694586431</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-10.69474023738875</v>
+        <v>-10.67702456762814</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-8.46629382314029</v>
+        <v>-8.449251588301969</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-8.435378706357319</v>
+        <v>-8.418184458004951</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.444761554579046</v>
+        <v>-5.428616845065285</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.195040222302652</v>
+        <v>-5.205469858000804</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>199</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.02221053636633</v>
+        <v>-3.009688246690708</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.152807516277846</v>
+        <v>-3.139897706701795</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.039252304770599</v>
+        <v>-1.026245173352997</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.365141602194463</v>
+        <v>1.108211009113184</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.597169090736614</v>
+        <v>1.338324868520068</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.397424160253308</v>
+        <v>2.410467056547674</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3073746321079867</v>
+        <v>0.3200652349874318</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.34537955658574</v>
+        <v>2.357547401355255</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.294657571791959</v>
+        <v>5.305749489837517</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.445049448959992</v>
+        <v>5.456536354701889</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>5.240149600727683</v>
+        <v>5.251906411993588</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.761814252407831</v>
+        <v>2.774858573098093</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6221584111030154</v>
+        <v>0.3436366843486098</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.374392306193371</v>
+        <v>1.363962670495219</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.022407684976294</v>
+        <v>-3.28227908345773</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.628644549087902</v>
+        <v>-4.888130989718341</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.024783910173063</v>
+        <v>-5.28417241895027</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6062317346881017</v>
+        <v>-0.8424600114021459</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.6075513962663024</v>
+        <v>-0.8407499942534997</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.992821786145612</v>
+        <v>-3.240579717991324</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.004141604413064</v>
+        <v>-2.245544945663958</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.933585598036956</v>
+        <v>-2.171909786075453</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.068667320854857</v>
+        <v>-3.312229867490117</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.844613005605837</v>
+        <v>-3.082102623440122</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3638564558898949</v>
+        <v>-0.5879307388045021</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.480578278540939</v>
+        <v>-2.715033370410879</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.287929663679265</v>
+        <v>-1.515582568213901</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.113477148607402</v>
+        <v>-2.370927999068449</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.757149010986964</v>
+        <v>-2.472194255903368</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.817627323316437</v>
+        <v>-3.535248551444575</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.9456842696872343</v>
+        <v>-0.6809701067720724</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2723788986965161</v>
+        <v>-0.01065236662510927</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.354459375717887</v>
+        <v>-1.089641248427483</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.782598030543333</v>
+        <v>-3.50304464810597</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.05207090754153398</v>
+        <v>0.206392958836858</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.334037161373502</v>
+        <v>-4.05209068881144</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.668669220280606</v>
+        <v>-1.402599874417845</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.4264794811778</v>
+        <v>-1.165800737361543</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.632245573620096</v>
+        <v>-1.371213580324486</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.5063142207232048</v>
+        <v>-0.2511938178759294</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.019465006531483</v>
+        <v>-1.759413355523321</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.316191761686646</v>
+        <v>-2.077155966166238</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>178</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.641112434205105</v>
+        <v>-8.628590144529483</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.326284996102459</v>
+        <v>-6.313375186526407</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.365056326670434</v>
+        <v>-3.352049195252832</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-5.476362783524948</v>
+        <v>-5.463383641126484</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.893637026915329</v>
+        <v>-4.880526222540389</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.19605511639515</v>
+        <v>-10.18301222010079</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-14.20649887872844</v>
+        <v>-14.18567856056455</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-12.43632717317569</v>
+        <v>-12.4158606290646</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-13.62601216807882</v>
+        <v>-13.60474130142729</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-12.79910179772984</v>
+        <v>-12.77770322781166</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-13.57317871632429</v>
+        <v>-13.55117237736732</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-9.614805655609921</v>
+        <v>-9.594558424431696</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.102475996891897</v>
+        <v>-6.088919950540294</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.852754664615745</v>
+        <v>-5.863184300313897</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>172</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7405909773872494</v>
+        <v>-0.7280686877116267</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.184351146142603</v>
+        <v>5.197260955718654</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.309670884438866</v>
+        <v>1.322678015856468</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.457593214972611</v>
+        <v>-1.444614072574147</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.573807339126191</v>
+        <v>-2.560696534751251</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.434201926576485</v>
+        <v>-3.421159030282119</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.939323735972799</v>
+        <v>-2.924025207860879</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.565258797789973</v>
+        <v>-4.548229676928294</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.209856762161316</v>
+        <v>-5.19219992958358</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.901318425406629</v>
+        <v>-4.883218742021178</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.853608684884804</v>
+        <v>-6.834014905277499</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.081228441081564</v>
+        <v>-5.062377160262322</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.082878400863748</v>
+        <v>-6.069322354512146</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.926180324401351</v>
+        <v>-2.936609960099503</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>177</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.318697730861324</v>
+        <v>-3.306175441185701</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4243343324437703</v>
+        <v>-0.4114245228677191</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.198726378238987</v>
+        <v>-4.185719246821385</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.631821243047881</v>
+        <v>-4.618842100649417</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.480763111170326</v>
+        <v>-3.467652306795387</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9321877649862813</v>
+        <v>-0.9191448686919159</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4523023102077772</v>
+        <v>-0.4382486493447146</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.042641815324849</v>
+        <v>-2.026473107333722</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.105837361178672</v>
+        <v>-2.089310561248318</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1364447816328394</v>
+        <v>-0.1206288628147973</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.785922148281081</v>
+        <v>0.801496997146252</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2531560024869535</v>
+        <v>0.2694834089822749</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.297042111282742</v>
+        <v>-1.283486064931139</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.4823490275940969</v>
+        <v>-0.4927786632922491</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>177</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.995634093583362</v>
+        <v>4.008156383258985</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.075223132069659</v>
+        <v>4.088132941645711</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.114559789262167</v>
+        <v>3.127566920679769</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.557675789772169</v>
+        <v>1.570654932170633</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.789956965894049</v>
+        <v>-1.77684616151911</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.7560252644722638</v>
+        <v>0.7690681607666292</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.826232758076543</v>
+        <v>-3.809063220752748</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9127666409436301</v>
+        <v>-0.8966584269527758</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.102766056938563</v>
+        <v>-2.08525429281601</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.827027446598805</v>
+        <v>-1.809077297296604</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.035915002000856</v>
+        <v>-2.017341453156618</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.831589760224908</v>
+        <v>-4.810134170994225</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.991957365520094</v>
+        <v>-2.978401319168491</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.742236033243806</v>
+        <v>-2.752665668941958</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>161</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.34275787019196</v>
+        <v>7.355280159867583</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.621518257037046</v>
+        <v>2.634428066613097</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.38051880921887</v>
+        <v>0.3935259406364722</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.348471371990449</v>
+        <v>-1.335492229591985</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.197859525197075</v>
+        <v>1.210970329572014</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.500546491950942</v>
+        <v>1.513589388245308</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.743134442466058</v>
+        <v>1.405276398307642</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.357148004106307</v>
+        <v>4.369812084601847</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.806835446972947</v>
+        <v>1.822687127636478</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.79899654321089</v>
+        <v>3.436819334445218</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4834328727487289</v>
+        <v>0.501613267807187</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.8988380041012292</v>
+        <v>0.5250049438991553</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.099701405578614</v>
+        <v>1.113257451930217</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.135049311834536</v>
+        <v>-1.145478947532688</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>137</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.006869555688844287</v>
+        <v>0.01939184536446703</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.292146230207187</v>
+        <v>1.305056039783238</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.282214776253696</v>
+        <v>-1.269207644836094</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.886292887508255</v>
+        <v>-1.87331374510979</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.159045346442412</v>
+        <v>-3.145934542067472</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.127272164864763</v>
+        <v>-2.114229268570398</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.868253610496872</v>
+        <v>2.881319864797348</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.109745959818937</v>
+        <v>3.12377539805491</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.465728765151155</v>
+        <v>3.044936804654384</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.877164304517287</v>
+        <v>1.890569432170118</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.385831280540835</v>
+        <v>0.9467196426116686</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7695665840115424</v>
+        <v>-0.7561142952914324</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.459894187657099</v>
+        <v>-0.4463381413054961</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9400998626800785</v>
+        <v>-0.9505294983782306</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>124</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.34422599882663</v>
+        <v>2.356748288502253</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.539659639707658</v>
+        <v>1.552569449283709</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.949754558406582</v>
+        <v>1.962761689824184</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.140868624442405</v>
+        <v>-1.12788948204394</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.900166154970975</v>
+        <v>-4.887055350596036</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.603454084594667</v>
+        <v>-4.590411188300301</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.464975910924615</v>
+        <v>-1.451909656624139</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.936717448960714</v>
+        <v>-1.916934671860879</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4216375035666644</v>
+        <v>0.4348362425214276</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.377963931442018</v>
+        <v>0.3913690590948491</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.246144231585191</v>
+        <v>-2.232686937874973</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2075937644698271</v>
+        <v>0.2210460531899372</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.206693992234598</v>
+        <v>2.220250038586201</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.649963711607661</v>
+        <v>1.639534075909509</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>140</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.913514810200887</v>
+        <v>-3.900992520525264</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.383570092106559</v>
+        <v>-3.370660282530508</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.631861417750819</v>
+        <v>-6.618854286333217</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.212890558801178</v>
+        <v>-7.199911416402713</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.470555830970703</v>
+        <v>-3.457445026595764</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.461002267155486</v>
+        <v>-2.44795937086112</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.970581250958048</v>
+        <v>-3.957514996657572</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1625239005736034</v>
+        <v>-0.1427910069895688</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.9378095010416274</v>
+        <v>-0.9246107620868642</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.216506114641028</v>
+        <v>-3.203100986988197</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2357023211295086</v>
+        <v>-0.2221462747779057</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7002667031388867</v>
+        <v>-0.7106963388370389</v>
       </c>
     </row>
     <row r="30">
@@ -1823,98 +1823,98 @@
         <v>112</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.050351488707292</v>
+        <v>5.062873778382915</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.643111360729328</v>
+        <v>1.65602117030538</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3553855112755997</v>
+        <v>0.3683926426932018</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.25713545916971</v>
+        <v>2.270114601568174</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9641224256021417</v>
+        <v>-0.9510116212272024</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.229578577058533</v>
+        <v>-4.216535680764167</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1371776965699567</v>
+        <v>0.1502439508704327</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6982381862879024</v>
+        <v>-1.221055812115488</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.328740561041442</v>
+        <v>5.34219785475166</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.148838004101108</v>
+        <v>7.162290292821218</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.835726250299167</v>
+        <v>5.84928229665077</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.299733296861106</v>
+        <v>4.289303661162954</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 86.4</t>
+          <t>X ≈ 86.39</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>130</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.352715525943822</v>
+        <v>1.365237815619444</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.048834220671921</v>
+        <v>2.061744030247972</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.422957562847742</v>
+        <v>-1.40995043143014</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.322680185144364</v>
+        <v>3.335659327542828</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.861182046995239</v>
+        <v>5.874292851370178</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.620162446249402</v>
+        <v>4.633205342543768</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.99696719051564</v>
+        <v>3.010033444816116</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.145168407118717</v>
+        <v>7.158349416413955</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.853399290167161</v>
+        <v>7.866598029121924</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.003274105139234</v>
+        <v>7.016679232792065</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.106213088513982</v>
+        <v>9.1196703822242</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.371365476628625</v>
+        <v>8.384817765348735</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>8.720341634914497</v>
+        <v>8.7338976812661</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.200832197960011</v>
+        <v>8.190402562261859</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>117</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.335621508849854</v>
+        <v>7.348143798525477</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.305244477082177</v>
+        <v>2.318154286658228</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.474478334588156</v>
+        <v>4.487485466005758</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3312271936914044</v>
+        <v>0.3442063360898686</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.647506833320044</v>
+        <v>0.6606176376949833</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.7644529383660128</v>
+        <v>-0.7514100420716474</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.413289219740854</v>
+        <v>-3.400222965440378</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.025771763821503</v>
+        <v>-3.012590754526265</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.505575068807197</v>
+        <v>-6.492376329852434</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.577547595246713</v>
+        <v>-1.564090301536496</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.585040690303863</v>
+        <v>3.598492979023973</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.874187788760629</v>
+        <v>4.887743835112232</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.123909121036917</v>
+        <v>5.113479485338765</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>103</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.06625385419054908</v>
+        <v>-0.05373156451492633</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.677827467154813</v>
+        <v>-1.664917657578762</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.014443746566926</v>
+        <v>-4.001436615149323</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.0006954683283808549</v>
+        <v>0.01228367407008335</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.509990469808301</v>
+        <v>-1.496879665433362</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7291990407228965</v>
+        <v>0.7422419370172619</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.440581828304971</v>
+        <v>7.453648082605447</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.031650856707927</v>
+        <v>5.044831866003165</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.85414611615672</v>
+        <v>8.867344855111483</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.91664229035209</v>
+        <v>10.93004741800492</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>14.59538411166557</v>
+        <v>14.60884140537578</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>14.62976726901103</v>
+        <v>14.64321955773114</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>13.23863887165836</v>
+        <v>13.25219491800996</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.54661263111912</v>
+        <v>11.53618299542097</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>81</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.6415864683581347</v>
+        <v>-0.629064178682512</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.919679424850464</v>
+        <v>3.932589234426516</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.22851442195757</v>
+        <v>7.241521553375172</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.655063850861346</v>
+        <v>3.66804299325981</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.52405004319662</v>
+        <v>10.53716084757156</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9.586924079677701</v>
+        <v>9.599966975972066</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.502190362405422</v>
+        <v>9.515256616705898</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.800439062389366</v>
+        <v>7.813620071684603</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>17.61598238608361</v>
+        <v>17.62918112503837</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.53128929982111</v>
+        <v>15.54469442747394</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.3265359755035</v>
+        <v>15.33999326921372</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.5337586390218</v>
+        <v>21.54721092774191</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19.87893612684231</v>
+        <v>19.89249217319392</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.89408955788402</v>
+        <v>18.88365992218586</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-7 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-7 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1275846616733887</v>
+        <v>-0.1278314170254475</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1162341825033408</v>
+        <v>-0.1164923675006193</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2051026993120644</v>
+        <v>-0.2053414273578582</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.06159724111499543</v>
+        <v>-0.06187042430610035</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1228924722354918</v>
+        <v>-0.123153685495403</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.007432181345230049</v>
+        <v>-0.007720138225465689</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.01887542395288477</v>
+        <v>0.01858045336307157</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01959695212504187</v>
+        <v>-0.01988514823977994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.006192733283185703</v>
+        <v>0.005897771646687033</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.04954829049922438</v>
+        <v>0.04923807180251316</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.05411604130689085</v>
+        <v>0.05380346986497386</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1022757988815783</v>
+        <v>0.1019514873724319</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1605794792619264</v>
+        <v>0.1602385206663683</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1550585441609158</v>
+        <v>0.1552527805367419</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4043</v>
+        <v>4044</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.225193744273092</v>
+        <v>-0.2255549262701209</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2455791341606712</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3558253857007685</v>
+        <v>-0.3561706723482914</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1875401644542123</v>
+        <v>-0.1879261151348643</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2930437864013342</v>
+        <v>-0.2934081867971372</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05617577982963695</v>
+        <v>-0.05659646473089452</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.07805655117483212</v>
+        <v>-0.07847271700534009</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1365915716034962</v>
+        <v>-0.1369972122660315</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.08518386580729498</v>
+        <v>-0.08560289418296918</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.01728258245387337</v>
+        <v>0.01683125468322544</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.02411871230194151</v>
+        <v>0.02366384366760599</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.04769903182497615</v>
+        <v>0.04723838970707561</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.08646809006172163</v>
+        <v>0.08599428676195942</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.05341691228106527</v>
+        <v>0.05375187368239409</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.201460243478536</v>
+        <v>-0.2019621077448122</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1802673530596053</v>
+        <v>-0.1807917100456109</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2625925041776043</v>
+        <v>-0.2631007697536702</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1437486739546472</v>
+        <v>-0.1442854534986608</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2447070763502026</v>
+        <v>-0.2452246294038076</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1082371162733864</v>
+        <v>-0.1087858333626244</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1045221385186608</v>
+        <v>-0.1050729504100687</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.08391147232304519</v>
+        <v>-0.08447263179733966</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1311623289426365</v>
+        <v>-0.1317126195505836</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.04368642496736186</v>
+        <v>-0.04426780818492659</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.00967102737015324</v>
+        <v>-0.01026335445112636</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.03617502184366828</v>
+        <v>-0.03676065622968139</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.03237792446203258</v>
+        <v>0.03177043055028861</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.003655141743521995</v>
+        <v>-0.003192947675479729</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3239381933386269</v>
+        <v>-0.3246501756383608</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3232860448493611</v>
+        <v>-0.3240229558742556</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.5014038690168192</v>
+        <v>-0.502101934749156</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3066513771480857</v>
+        <v>-0.3073972858108078</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.272539451216943</v>
+        <v>-0.273302569968223</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.164468573137718</v>
+        <v>-0.1652550236077346</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.05747519048334482</v>
+        <v>-0.0582905076542346</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.002381551819162553</v>
+        <v>-0.003218367771381736</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1256341350905146</v>
+        <v>-0.1264409603583445</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.07161438378791019</v>
+        <v>-0.07244826823475137</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.04314438413261712</v>
+        <v>0.04227778499435431</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.0099224466440333</v>
+        <v>-0.01077544835691668</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1186226615996944</v>
+        <v>0.1177301338008405</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.02453205082581889</v>
+        <v>-0.02386217529124934</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3831</v>
+        <v>3832</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5683602765055014</v>
+        <v>-0.5693425584927354</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5791207023649676</v>
+        <v>-0.5801354222454265</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7778608584069531</v>
+        <v>-0.7788329150667224</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5294817117975299</v>
+        <v>-0.5305161419642346</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4288820555688275</v>
+        <v>-0.4299548405369364</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3256367402374636</v>
+        <v>-0.32673055489213</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1617292459296849</v>
+        <v>-0.1628681521543029</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1455835826168723</v>
+        <v>-0.1467373675681074</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.06189709228249995</v>
+        <v>-0.06307459171566165</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.06321872406545737</v>
+        <v>-0.06441485560129223</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.05962587291266885</v>
+        <v>0.05839267687868244</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.004350284672135274</v>
+        <v>0.003131637183741987</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1467909684619499</v>
+        <v>0.1455254482291082</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.0197989268719283</v>
+        <v>0.02073819739916871</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3733</v>
+        <v>3734</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6514735577967343</v>
+        <v>-0.652786860531684</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6737702776335155</v>
+        <v>-0.6751240136142016</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9475302124203964</v>
+        <v>-0.9488227740408064</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.589237445715284</v>
+        <v>-0.590622723739223</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4184709563349074</v>
+        <v>-0.4199178804573975</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4005025343193438</v>
+        <v>-0.4019465712826502</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1766239242520058</v>
+        <v>-0.1781309702930187</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1478140851149377</v>
+        <v>-0.1493428912783656</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.113839463588441</v>
+        <v>-0.1153798752951332</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.06615633062783388</v>
+        <v>-0.0677344808351279</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.0652807874103587</v>
+        <v>0.06366083116513011</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.007654221351103274</v>
+        <v>0.006049852319577553</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.05774017638373863</v>
+        <v>0.05610960588766289</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.0255891171299325</v>
+        <v>-0.02433931075531603</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3609</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.5331953605191941</v>
+        <v>-0.5482821266138629</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5286518116608434</v>
+        <v>-0.5433586825597985</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8258474905995499</v>
+        <v>-0.8404646685742208</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4873395823221998</v>
+        <v>-0.501992382449302</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3751576221802111</v>
+        <v>-0.3896863976836613</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1455805196594468</v>
+        <v>-0.1601848448193266</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1442612681193935</v>
+        <v>0.1296726551632261</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2454982294402228</v>
+        <v>0.2310167214463874</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.0614789802612421</v>
+        <v>0.04700754766094661</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2507351964973665</v>
+        <v>0.2364624940920734</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4491724547291511</v>
+        <v>0.4349442556375891</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3607994710473861</v>
+        <v>0.3465585999779677</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5379423167811055</v>
+        <v>0.5237975321077784</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3601774246369089</v>
+        <v>0.3497477889387568</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4370678859275472</v>
+        <v>-0.4395129253014574</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.4801557766725111</v>
+        <v>-0.4826687039835775</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.8020389131521242</v>
+        <v>-0.8044799525419393</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.7714697639278612</v>
+        <v>-0.77391455181521</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6034129606460894</v>
+        <v>-0.6059338879238823</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1463210702341229</v>
+        <v>-0.1489603754123365</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1001229852262782</v>
+        <v>-0.1027811599340254</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1688882031727914</v>
+        <v>0.1661281545297584</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.02029519061870388</v>
+        <v>-0.02300516307492018</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2123948575125922</v>
+        <v>0.209574547336274</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3988402767281158</v>
+        <v>0.3959546515880348</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2764655698418181</v>
+        <v>0.2736154401285305</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3920033065761714</v>
+        <v>0.3890976457563085</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2251704463167385</v>
+        <v>0.2272545991138983</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5761225622710882</v>
+        <v>-0.5636002725954654</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4640170275703994</v>
+        <v>-0.4671770187449766</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.8888527704270999</v>
+        <v>-0.8758456390094977</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8924092817436602</v>
+        <v>-0.8954556767217028</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8750652139896147</v>
+        <v>-0.8781513471171465</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4414406177531873</v>
+        <v>-0.4446403499945859</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5699279605379814</v>
+        <v>-0.5730960831245113</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1805311034547614</v>
+        <v>-0.1838463416234006</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.225024837491425</v>
+        <v>-0.2283322506822998</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0524771543422915</v>
+        <v>0.04903264941447105</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2851302962686617</v>
+        <v>0.2816015441553503</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2764135535516985</v>
+        <v>0.2728876408022103</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.2939468694755476</v>
+        <v>0.290388065881487</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3503303246078744</v>
+        <v>0.3528959150167097</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3169</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.6532369990397981</v>
+        <v>-0.6407147093641754</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5976196714567052</v>
+        <v>-0.5847098618806541</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6779240496481478</v>
+        <v>-0.6649169182305457</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9397974253508679</v>
+        <v>-0.9436254015688803</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.8948287033497451</v>
+        <v>-0.8987138775836456</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3914632076936329</v>
+        <v>-0.3954864566862781</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4906160923432878</v>
+        <v>-0.4946168167611589</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.121566118595041</v>
+        <v>-0.1257208440342836</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2282511740865161</v>
+        <v>-0.2323792380973089</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1684695654166646</v>
+        <v>0.1641494744948986</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2652747773769732</v>
+        <v>0.2609061955911471</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1597663502030002</v>
+        <v>0.1554312578165309</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4515356538964639</v>
+        <v>0.4470740947579657</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4172557239449191</v>
+        <v>0.4068260882467669</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>3009</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3900928415746634</v>
+        <v>-0.3775705518990407</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6436008699082478</v>
+        <v>-0.6306910603321967</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6409869663690344</v>
+        <v>-0.6279798349514323</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.9567713110069249</v>
+        <v>-0.9614844031881731</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.112887966517896</v>
+        <v>-1.117601933765123</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9302354317346797</v>
+        <v>-0.9349851676421039</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.963997218210018</v>
+        <v>-0.9687463960327491</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5838908547872848</v>
+        <v>-0.5888122113447096</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4276392862580778</v>
+        <v>-0.4326210000241062</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1016498329970332</v>
+        <v>0.09641065304788299</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3140918918759965</v>
+        <v>0.3087601768916741</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5001669077556343</v>
+        <v>0.4947735684297498</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8631439970588346</v>
+        <v>0.8575879444912431</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7805290049748592</v>
+        <v>0.7700993692767071</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2850</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3256061523778015</v>
+        <v>-0.3130838627021788</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5385783667406656</v>
+        <v>-0.5256685571646145</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.863517003407182</v>
+        <v>-0.8505098719895798</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.169207779985982</v>
+        <v>-1.174830182946671</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.234150891584683</v>
+        <v>-1.239813748570597</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.127932650813143</v>
+        <v>-1.133603076468994</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.9838559079545774</v>
+        <v>-0.9895896132599233</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.5915957044265028</v>
+        <v>-0.5975221629870617</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4582820208133711</v>
+        <v>-0.4642655031426486</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.04271976288142554</v>
+        <v>0.0364625328837036</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2783999479378565</v>
+        <v>0.2720336166063433</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4378468731696543</v>
+        <v>0.4314247348168578</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5988841450359459</v>
+        <v>0.5923549027538328</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.4626405650315348</v>
+        <v>0.4522109293333827</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2666</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2512858538422691</v>
+        <v>-0.2387635641666463</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2186143248035251</v>
+        <v>-0.2057045152274739</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.7255906547185091</v>
+        <v>-0.712583523300907</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.7995340492193961</v>
+        <v>-0.8065736263493122</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.243127256266909</v>
+        <v>-1.250078104776442</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.187486694733074</v>
+        <v>-1.194422526968921</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.139951280235231</v>
+        <v>-1.146920712138098</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.6136657949951783</v>
+        <v>-0.6208997775059188</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4295162961192034</v>
+        <v>-0.4368319740459938</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.01477365841473954</v>
+        <v>0.007171886206066347</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4307431311849399</v>
+        <v>0.4229530867807725</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8238473779294324</v>
+        <v>0.8159099115833115</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9501298511993284</v>
+        <v>0.9420831965382348</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9747949194096037</v>
+        <v>0.9643652837114516</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2461</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2667176724366911</v>
+        <v>-0.2541953827610683</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.05642893722281173</v>
+        <v>-0.04351912764676058</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6537267936169755</v>
+        <v>-0.6407196621993734</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4611625415902125</v>
+        <v>-0.4700086886515038</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6130730334186296</v>
+        <v>-0.6219529036847717</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.004447951456619</v>
+        <v>-0.9914050551622537</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6621017502720505</v>
+        <v>-0.6709290286909919</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.09358634988423375</v>
+        <v>-0.1027275690246299</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3545695195321201</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.9068705087356363</v>
+        <v>0.8971598069846181</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.171861609704514</v>
+        <v>1.162003049556859</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.595136019651811</v>
+        <v>1.585105094746908</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.482820927259695</v>
+        <v>1.472759144741694</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.488738927557108</v>
+        <v>1.478309291858956</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2262</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.02430251774084269</v>
+        <v>-0.01178022806521994</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.215975721146755</v>
+        <v>0.2288855307228062</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6198100930336068</v>
+        <v>-0.6068029616160047</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.62183209270124</v>
+        <v>-0.6088529503027758</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8075196217063905</v>
+        <v>-0.7944088173314512</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.303728477641528</v>
+        <v>-1.290685581347162</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7473916707378478</v>
+        <v>-0.7581119899960456</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3081549685347795</v>
+        <v>-0.319170857753889</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.08003592803626702</v>
+        <v>-0.09117235583293137</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5076231130218147</v>
+        <v>0.4960475465974667</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8139529844995508</v>
+        <v>0.8021928067960715</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.492497218450026</v>
+        <v>1.480436243203187</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.558537921386652</v>
+        <v>1.572093967738255</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.498798599374695</v>
+        <v>1.488368963676542</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2443138411733159</v>
+        <v>0.2795256401329524</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6500312944914697</v>
+        <v>0.684662158686983</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2251448088390262</v>
+        <v>-0.1901860383580214</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6232298126388258</v>
+        <v>-0.5880453882886272</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8254358499972554</v>
+        <v>-0.7902811727813344</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.152393528035674</v>
+        <v>-1.117006999123205</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.6347926882409354</v>
+        <v>-0.6256251836414179</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1625239005736034</v>
+        <v>-0.1541459652457107</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1877316244994987</v>
+        <v>0.1957297335539678</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8079679675809359</v>
+        <v>0.8147561558689915</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9194792638407989</v>
+        <v>0.9260121885659913</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.848466410376957</v>
+        <v>1.854129973833231</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.813568254152678</v>
+        <v>1.847115710227982</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.822441802228582</v>
+        <v>1.832119535707285</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1893</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5344711058037106</v>
+        <v>0.5469933954793333</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.08192856182314</v>
+        <v>1.094838371399192</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1554888546207422</v>
+        <v>-0.1424817232031401</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6571472543987085</v>
+        <v>-0.6441681120002443</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7742941145472386</v>
+        <v>-0.7611833101722993</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.8981265317552172</v>
+        <v>-0.8850836354608518</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.6911255386730417</v>
+        <v>-0.7064975228997383</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.240744417823862</v>
+        <v>0.2247350855393293</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.3671935128221477</v>
+        <v>0.3510877091835596</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.023976358031462</v>
+        <v>1.007266704392194</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.166159477921809</v>
+        <v>1.149303018716985</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.076107644128321</v>
+        <v>2.058767891252401</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.184115051144332</v>
+        <v>2.197671097495935</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.22253157623625</v>
+        <v>2.212101940538098</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1715</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.486805723950397</v>
+        <v>1.49932801362602</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.850827694948954</v>
+        <v>1.863737504525005</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1776324340234794</v>
+        <v>0.1906395654410815</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1569604531249666</v>
+        <v>-0.1439813107265024</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3467471533801785</v>
+        <v>-0.3336363490052392</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.06690628927447051</v>
+        <v>0.0799491855688359</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.7116362423939293</v>
+        <v>0.6925078559366113</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.556498787035466</v>
+        <v>1.536703620349535</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.819549554338387</v>
+        <v>1.799564422821305</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.458674848833518</v>
+        <v>2.438009939338137</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.695956678257559</v>
+        <v>2.675066645832445</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.289508558037014</v>
+        <v>3.26826764879862</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.044181060794735</v>
+        <v>3.057737107146338</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.060666241467523</v>
+        <v>3.050236605769371</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1543</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.735096218201903</v>
+        <v>1.747618507877526</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.479235968697942</v>
+        <v>1.492145778273994</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.05144279470302848</v>
+        <v>0.06444992612063061</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.01197741032665078</v>
+        <v>0.001001732071813421</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.09849417091205481</v>
+        <v>-0.08538336653711553</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4571788836531852</v>
+        <v>0.4702217799475505</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.118612986579983</v>
+        <v>1.095646992017734</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.238898206730845</v>
+        <v>2.214998193992948</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.603125631096617</v>
+        <v>2.578944506174281</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.279101837277658</v>
+        <v>3.254115793643898</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.760457807525526</v>
+        <v>3.735054997608799</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.222604322034684</v>
+        <v>4.196894289860502</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.061584967084599</v>
+        <v>4.075141013436202</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.728026973372543</v>
+        <v>3.717597337674391</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1366</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.389943603988272</v>
+        <v>2.402465893663894</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.725891856913229</v>
+        <v>1.73880166648928</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6021601765556994</v>
+        <v>0.6151673079733015</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.5866407144110255</v>
+        <v>0.5996198568094897</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.3397646888432249</v>
+        <v>0.3528754932181641</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6372066265588856</v>
+        <v>0.650249522853251</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.322164968667408</v>
+        <v>1.294402137348015</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.793680478988435</v>
+        <v>2.764588545628989</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.213291406816033</v>
+        <v>3.18383553614045</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.721672665643062</v>
+        <v>3.691399691296311</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.145884463225578</v>
+        <v>4.115171956673123</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.736947186280617</v>
+        <v>4.705790136065069</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.755931228337175</v>
+        <v>4.769487274688778</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.273588138944362</v>
+        <v>4.26315850324621</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1189</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.150913144225171</v>
+        <v>2.163435433900794</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.376159614942928</v>
+        <v>1.389069424518979</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.2281528330325244</v>
+        <v>0.2411599644501266</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4420879740082313</v>
+        <v>0.4550671164066955</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6568048342498685</v>
+        <v>0.6699156386248077</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6195187384927223</v>
+        <v>0.6325616347870877</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.08857909619784</v>
+        <v>2.054127426148533</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.345439217615834</v>
+        <v>3.309618582758482</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.00466413270717</v>
+        <v>3.968216444235736</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.547677644504986</v>
+        <v>4.510225954526717</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.066135519024634</v>
+        <v>5.028086063939618</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.161363535760408</v>
+        <v>6.122374326434709</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.909317503453025</v>
+        <v>5.922873549804628</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.317995942541756</v>
+        <v>5.307566306843604</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1028</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.337793493563062</v>
+        <v>1.350315783238685</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.181118037727799</v>
+        <v>1.19402784730385</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2042900682796116</v>
+        <v>0.2172971996972137</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.7225160427881789</v>
+        <v>0.7354951851866431</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5720676696170841</v>
+        <v>0.5851784739920234</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4815367654316702</v>
+        <v>0.4945796617260356</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.142680836714199</v>
+        <v>2.155747091014675</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.186990662533184</v>
+        <v>3.143576604356937</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.348876601971007</v>
+        <v>4.304238058994969</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.664932174960569</v>
+        <v>4.6783373026134</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.783854513237102</v>
+        <v>5.736998632205498</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.985552845679806</v>
+        <v>6.999005134399916</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.662574499326347</v>
+        <v>6.67613054567795</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.328638244053998</v>
+        <v>6.318208608355846</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>891</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.54243611925191</v>
+        <v>1.554958408927533</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.16404636278989</v>
+        <v>1.176956172365941</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4328547862381527</v>
+        <v>0.4458619176557548</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.123646035437574</v>
+        <v>1.136625177836038</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.145762936957325</v>
+        <v>1.158873741332265</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.882666758081065</v>
+        <v>0.8957096543754304</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.03111689731103</v>
+        <v>2.044183151611506</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.198867794151418</v>
+        <v>3.146621234282165</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.484669254770459</v>
+        <v>4.497867993725222</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.093578862110661</v>
+        <v>5.106983989763492</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.460093775727991</v>
+        <v>6.473551069438209</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.177978616575103</v>
+        <v>8.191430905295213</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.757724005630202</v>
+        <v>7.771280051981805</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.446278110072591</v>
+        <v>7.435848474374438</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>767</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.412811679790025</v>
+        <v>1.425333969465647</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.103321400159103</v>
+        <v>1.116231209735155</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1876193602291778</v>
+        <v>0.2006264916467799</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.489747492836678</v>
+        <v>1.502726635235142</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.123201277764508</v>
+        <v>2.136312082139447</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.769601548813505</v>
+        <v>1.78264444510787</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.596326164874554</v>
+        <v>2.60939241917503</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.029131901251681</v>
+        <v>3.965240442054963</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.1415348833875</v>
+        <v>5.154733622342263</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.855946856117065</v>
+        <v>5.869351983769896</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.867621171955946</v>
+        <v>7.881078465666164</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.466541487058876</v>
+        <v>9.479993775778986</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.655152586674596</v>
+        <v>8.668708633026199</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.383361533031717</v>
+        <v>8.372931897333565</v>
       </c>
     </row>
     <row r="30">
@@ -3465,98 +3465,98 @@
         <v>627</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.602103081063909</v>
+        <v>2.614625370739532</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.10517914962832</v>
+        <v>2.118088959204371</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.71031044303173</v>
+        <v>1.723317574449332</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.432920263537319</v>
+        <v>3.445899405935783</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.372206054834571</v>
+        <v>3.38531685920951</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.714233979811375</v>
+        <v>2.727276876105741</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.062621281647381</v>
+        <v>4.075687535947857</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.965067805965461</v>
+        <v>4.882504242479591</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.498964251521599</v>
+        <v>6.512162990476362</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.881693930927483</v>
+        <v>7.895099058580314</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.633878405652965</v>
+        <v>8.647335699363182</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.74162679425837</v>
+        <v>10.75507908297848</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.64035144966116</v>
+        <v>10.65390749601276</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.4116038824159</v>
+        <v>10.40117424671775</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 84.83</t>
+          <t>X &gt; 84.82</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>515</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.069668475906525</v>
+        <v>2.082190765582148</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.205667678476253</v>
+        <v>2.218577488052304</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.004973729161215</v>
+        <v>2.017980860578817</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.688624920021141</v>
+        <v>3.701604062419605</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.315252248638288</v>
+        <v>4.328363053013227</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.224344671790845</v>
+        <v>4.237387568085211</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.916309983644787</v>
+        <v>4.929376237945263</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.196699400397264</v>
+        <v>6.209880409692502</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.494922815185838</v>
+        <v>7.508121554140601</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.58654520297344</v>
+        <v>8.599950330626271</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.352665665063626</v>
+        <v>9.366122958773843</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.52297115250616</v>
+        <v>11.53642344122627</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.6852408134059</v>
+        <v>11.69879685975751</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>11.74078738840065</v>
+        <v>11.7303577527025</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>385</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.311756484984826</v>
+        <v>2.324278774660449</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.258624430462127</v>
+        <v>2.271534240038179</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.162457022566841</v>
+        <v>3.175464153984443</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.812190674654858</v>
+        <v>3.825169817053322</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.793249979063205</v>
+        <v>3.806360783438144</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.090691916778866</v>
+        <v>4.103734813073231</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.564399757948145</v>
+        <v>5.577466012248621</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.876437138387423</v>
+        <v>5.889618147682661</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.373878810646687</v>
+        <v>7.38707754960145</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.121156223021359</v>
+        <v>9.13456135067419</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.435883418184289</v>
+        <v>9.449340711894507</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.58714969241285</v>
+        <v>12.60060198113296</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.68637560094846</v>
+        <v>12.69993164730006</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.93609693322475</v>
+        <v>12.92566729752659</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>268</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1185019782974877</v>
+        <v>0.1310242679731104</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.238271648915322</v>
+        <v>2.251181458491374</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.58967159903515</v>
+        <v>2.602678730452752</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.331865030150105</v>
+        <v>5.344844172548569</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.166578143436155</v>
+        <v>5.179688947811094</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.210288737868233</v>
+        <v>6.223331634162598</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.483763975819834</v>
+        <v>9.49683023012031</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.762849233754743</v>
+        <v>9.776030243049981</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>13.43319263115453</v>
+        <v>13.4463913701093</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.32933610284303</v>
+        <v>13.34274123049586</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>14.24398576360007</v>
+        <v>14.25744305731028</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.51717489109477</v>
+        <v>16.53062717981488</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.09692028014987</v>
+        <v>16.11047632650147</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>16.34664161242615</v>
+        <v>16.336211976728</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>165</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2338344070627443</v>
+        <v>0.246356696738367</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.682866854704557</v>
+        <v>4.695776664280608</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.712240572350382</v>
+        <v>6.725247703767984</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.660675523139702</v>
+        <v>8.673654665538166</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.334375520188757</v>
+        <v>9.347486324563697</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9.631817457904418</v>
+        <v>9.644860354198784</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.75920495275334</v>
+        <v>10.77227120705382</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.71626397821428</v>
+        <v>12.72944498750952</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.2916277283956</v>
+        <v>16.30482646735037</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.83544193730707</v>
+        <v>14.8488470649599</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.02462800692888</v>
+        <v>14.0380853006391</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>17.69537480063795</v>
+        <v>17.70882708935806</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>17.88118079575366</v>
+        <v>17.89473684210526</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.34302334015115</v>
+        <v>19.332593704453</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.418797590635293</v>
+        <v>5.431707400211344</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.214405074514886</v>
+        <v>6.227412205932488</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13.48751534997954</v>
+        <v>13.500494492378</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.187189373002603</v>
+        <v>8.200300177377542</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>17.45652371847401</v>
+        <v>17.46970472776925</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15.01457145133931</v>
+        <v>15.02777019029408</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>14.16444626631139</v>
+        <v>14.17785139396422</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>12.76921675151763</v>
+        <v>12.78267404522785</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>13.99407609933924</v>
+        <v>14.00752838805935</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>15.95477386934673</v>
+        <v>15.96832991569833</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>19.77592377305159</v>
+        <v>19.76549413735344</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-7 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-7 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>5.852417302798983</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.361285623235915</v>
+        <v>4.374466632531153</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.259684361549496</v>
+        <v>2.273089489202327</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2916381863750317</v>
+        <v>-0.2781858976549216</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.843123845996033</v>
+        <v>-2.853553481694185</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>128</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.881561679790025</v>
+        <v>6.894083969465647</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.176238066825768</v>
+        <v>9.189147876401819</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>11.12511936022918</v>
+        <v>11.13812649164678</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.567872492836678</v>
+        <v>6.580851635235142</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.935701277764508</v>
+        <v>9.948812082139447</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.201893215480169</v>
+        <v>3.214936111774534</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.67965949820789</v>
+        <v>4.692725752508366</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.556226099426389</v>
+        <v>6.569407108721627</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.713976213244088</v>
+        <v>5.727174952198851</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.52010102821616</v>
+        <v>2.533506155868992</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.315347703898581</v>
+        <v>2.328804997608799</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.568480861244012</v>
+        <v>1.581933149964122</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3669762502991105</v>
+        <v>0.3805322966507134</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.397947582575398</v>
+        <v>1.387517946877246</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>170</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.565385209201786</v>
+        <v>4.577907498877408</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.306752772708123</v>
+        <v>5.319662582284174</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.088354654346823</v>
+        <v>6.101361785764425</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.865666610483743</v>
+        <v>3.878645752882207</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.268421865999805</v>
+        <v>6.281532670374744</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.624687333127234</v>
+        <v>3.637730229421599</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.1281889099726</v>
+        <v>4.141255164273076</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.6610055111911</v>
+        <v>3.674186520486337</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.364711507361733</v>
+        <v>5.377910246316496</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.338115734098515</v>
+        <v>3.351520861751347</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.545127115663291</v>
+        <v>2.558584409373509</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.167745567126367</v>
+        <v>3.181197855846477</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.571020367946176</v>
+        <v>1.584576414297779</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.408976994340108</v>
+        <v>2.398547358641956</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>243</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.119730404069863</v>
+        <v>5.132252693745485</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.977292593574745</v>
+        <v>5.990202403150796</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.051559689447288</v>
+        <v>8.06456682086489</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.301154385840789</v>
+        <v>5.314133528239253</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.76273317076862</v>
+        <v>4.775843975143559</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.414084573504866</v>
+        <v>3.427127469799231</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.09478295499801</v>
+        <v>2.107849209298486</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.216076922471657</v>
+        <v>1.229257931766895</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.624212838758488</v>
+        <v>3.637411577713252</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.774087653730561</v>
+        <v>2.787492781383392</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.923243794433553</v>
+        <v>0.9367010881437707</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.780672219268709</v>
+        <v>1.794124507988819</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2856729266556215</v>
+        <v>-0.2721168803040186</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.021661574344947</v>
+        <v>2.011231938646795</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>340</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.330091091554735</v>
+        <v>6.342613381230358</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.071458655061065</v>
+        <v>7.084368464637116</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.735413477876236</v>
+        <v>8.748420609293838</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.218607786954323</v>
+        <v>6.231586929352787</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.212922627244879</v>
+        <v>4.225965523539244</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.657600674678477</v>
+        <v>2.670666928978953</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.484534922955795</v>
+        <v>2.497715932251033</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.835299742655849</v>
+        <v>1.848498481610612</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.867527498804399</v>
+        <v>1.880932626457231</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4863035862515233</v>
+        <v>0.499760879961741</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.108922037714599</v>
+        <v>1.122374326434709</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4878031614655924</v>
+        <v>-0.4742471151139895</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.938388759045985</v>
+        <v>0.9279591233478328</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>438</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.497429259698706</v>
+        <v>5.509951549374328</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.168960669565493</v>
+        <v>6.181870479141544</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>8.057196985799955</v>
+        <v>8.070204117217557</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.219413588727093</v>
+        <v>5.232392731125557</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.767750364522506</v>
+        <v>3.780861168897445</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.836881799955052</v>
+        <v>3.849924696249417</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.153974566701045</v>
+        <v>2.167040821001521</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.915101670202645</v>
+        <v>1.928282679497883</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.854101784020344</v>
+        <v>1.867300522975107</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.460597603558625</v>
+        <v>1.474002731211456</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3426022701086211</v>
+        <v>0.3560595638188389</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.8336064320202681</v>
+        <v>0.8470587207403781</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4133518210753664</v>
+        <v>0.4269078674269693</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.119694157917863</v>
+        <v>1.109264522219711</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.378447800786461</v>
+        <v>3.469350399305796</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.724169561487685</v>
+        <v>3.811983133950662</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.286596228556576</v>
+        <v>5.371030576904332</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.281618044438105</v>
+        <v>3.369816999355926</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.565260886305431</v>
+        <v>2.653907552832173</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.261279336476605</v>
+        <v>1.352702541614683</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.424877868340154</v>
+        <v>-0.3305868585040628</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.069997210182144</v>
+        <v>-0.9752753957188673</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2924904481195298</v>
+        <v>0.384701595182861</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.9135066230293916</v>
+        <v>-0.82045698800313</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.185875605709953</v>
+        <v>-2.090877506831696</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.617684619183038</v>
+        <v>-1.523639674192189</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.749683002369927</v>
+        <v>-2.654270101217847</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.610281954791148</v>
+        <v>-1.540434983850993</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>707</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.103449940044619</v>
+        <v>2.115972229720242</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.613517062582488</v>
+        <v>2.62642687215854</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.915960944387592</v>
+        <v>3.928968075805194</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.904771361294955</v>
+        <v>3.917750503693419</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.083464714822505</v>
+        <v>3.096575519197444</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.9763804856357581</v>
+        <v>0.9894233819301235</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.8916467683634792</v>
+        <v>0.9047130226639553</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4241929246188718</v>
+        <v>-0.411011915323634</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6463489147999582</v>
+        <v>0.6595476537547214</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.4866617016282504</v>
+        <v>-0.4732565739754193</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.398628604446543</v>
+        <v>-1.385171310736325</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.7984745843005356</v>
+        <v>-0.7850222955804256</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.360171910945589</v>
+        <v>-1.346615864593986</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5446797158687318</v>
+        <v>-0.5551093515668839</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>845</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.234694067496875</v>
+        <v>2.182602269347591</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.041560170844676</v>
+        <v>2.054469980420727</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.48828504070255</v>
+        <v>3.432748241055755</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.61853817331005</v>
+        <v>3.631517315708514</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.553489739302975</v>
+        <v>3.566600543677914</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.957440552758271</v>
+        <v>1.970483449052637</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.582766007083627</v>
+        <v>2.595832261384103</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.050493850905674</v>
+        <v>1.063674860200912</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.34452355052219</v>
+        <v>1.357722289476953</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2577119749617154</v>
+        <v>0.2711171026145465</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.6571005209534917</v>
+        <v>-0.6436432272432739</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6227173636080607</v>
+        <v>-0.6092650748879507</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.687942388754152</v>
+        <v>-0.6743863424025491</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.9115938375429451</v>
+        <v>-0.9220234732410972</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.033924863869629</v>
+        <v>1.992245003262859</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.07028687160664</v>
+        <v>2.027300861476448</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.130229031216217</v>
+        <v>2.086831670929655</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.058089342288326</v>
+        <v>3.071068484686791</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.918471716448458</v>
+        <v>2.931582520823397</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.421297502618756</v>
+        <v>1.434340398913122</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.835068271886854</v>
+        <v>1.84813452618733</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6699785919488193</v>
+        <v>0.6831596012440571</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.107483192306901</v>
+        <v>1.120681931261664</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1414455819533345</v>
+        <v>-0.1280404543005034</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.445899803578989</v>
+        <v>-0.4324425098687712</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.112413954309325</v>
+        <v>-0.09896166558921493</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.03117305179461</v>
+        <v>-1.017617005443007</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.925530461336777</v>
+        <v>-0.8915822525245503</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.982956529575425</v>
+        <v>0.9496157018841771</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.822823118372163</v>
+        <v>1.787726202582078</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.648012739420928</v>
+        <v>1.612782849035099</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.552126577101511</v>
+        <v>2.565105719499975</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.959535112674224</v>
+        <v>2.972645917049164</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.569100868102694</v>
+        <v>2.58214376439706</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.742320719188108</v>
+        <v>2.755386973488584</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.759230183691223</v>
+        <v>1.772411192986461</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.440276729151222</v>
+        <v>1.453475468105985</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.07424440740791027</v>
+        <v>0.08764953506074136</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.474447008053275</v>
+        <v>-0.4609897143430572</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9559709874232283</v>
+        <v>-0.9425186987031182</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.892132735083521</v>
+        <v>-1.878576688731918</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.681333828784325</v>
+        <v>-1.652841038505386</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6787671178564949</v>
+        <v>0.6511594411637631</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.299372042638311</v>
+        <v>1.270435640752268</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.854128437385</v>
+        <v>1.82453994591738</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.589525291626394</v>
+        <v>2.602504434024858</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.731890763392343</v>
+        <v>2.745001567767282</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.575474909882594</v>
+        <v>2.588517806176959</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.339455262201838</v>
+        <v>2.352521516502314</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.494057037399159</v>
+        <v>1.507238046694397</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.28177122080838</v>
+        <v>1.294969959763144</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2047171401677446</v>
+        <v>0.2181222678205756</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3026080449667745</v>
+        <v>-0.2891507512565568</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.646439713642522</v>
+        <v>-0.6329874249224119</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.9910513593831922</v>
+        <v>-0.9774953130315893</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6991852713231665</v>
+        <v>-0.6761166976008184</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4243335630791449</v>
+        <v>0.4017877468016309</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5067996129438868</v>
+        <v>0.483494693377942</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.277011790508055</v>
+        <v>1.253007049045586</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.473665985532556</v>
+        <v>1.48664512793102</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.263266018800373</v>
+        <v>2.276376823175312</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.228702644431038</v>
+        <v>2.241745540725404</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.21036998957576</v>
+        <v>2.223436243876236</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.278379153875264</v>
+        <v>1.291560163170502</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.018176080441954</v>
+        <v>1.031374819396717</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2344519578310411</v>
+        <v>0.2478570854838722</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5015098658225412</v>
+        <v>-0.4880525721123234</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.197538395064093</v>
+        <v>-1.184086106343983</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.418589818758001</v>
+        <v>-1.405033772406398</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.464386304467794</v>
+        <v>-1.44490237184786</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3653714814236366</v>
+        <v>0.3470723076580668</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1857061053546616</v>
+        <v>0.1669410502641284</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.9323623508833805</v>
+        <v>0.9130097374144341</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7121481937712559</v>
+        <v>0.7251273361697201</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9330727730916166</v>
+        <v>0.9461835774665559</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.555378019688234</v>
+        <v>1.535613681868</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.119972180849615</v>
+        <v>1.133038435150091</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3021166605017882</v>
+        <v>0.315297669797026</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2848914080300204</v>
+        <v>-0.2716926690752572</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.076571239463561</v>
+        <v>-1.06316611181073</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.4566606245643</v>
+        <v>-1.443203330854082</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.065176356757163</v>
+        <v>-2.051724068037053</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.900977431758164</v>
+        <v>-1.887421385406562</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.911628440816415</v>
+        <v>-1.895467149557582</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.0117808864706106</v>
+        <v>-0.003086087915683322</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1624531864379435</v>
+        <v>-0.1776971131597662</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7247797573033665</v>
+        <v>0.7089489459548801</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7793531514880172</v>
+        <v>0.7635188243678499</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.001993118768695</v>
+        <v>0.9858775552183872</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.642663754464991</v>
+        <v>1.626285484159474</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.03464379962076</v>
+        <v>1.047710053921236</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5151317770820683</v>
+        <v>0.5283127863773061</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2971460196281797</v>
+        <v>0.3103447585829429</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3959932941281608</v>
+        <v>-0.3825881664753297</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.757732489717327</v>
+        <v>-0.7442751960071092</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.560607312487022</v>
+        <v>-1.547155023766912</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.638095739229684</v>
+        <v>-1.653334134537147</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.56908358557547</v>
+        <v>-1.555872105478777</v>
       </c>
     </row>
     <row r="21">
@@ -4691,46 +4691,46 @@
         <v>2095</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.257472573302266</v>
+        <v>-0.2925240229225565</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5590814238929411</v>
+        <v>-0.5937679969918079</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2144050745148931</v>
+        <v>0.1797931583134442</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6565754466241955</v>
+        <v>0.6219128548635382</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8593487992135138</v>
+        <v>0.8247951612624291</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.231071803939876</v>
+        <v>1.196427528083539</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7648407094620708</v>
+        <v>0.7566570502182941</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2976573106805702</v>
+        <v>0.2895884064315553</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.001778436255193583</v>
+        <v>-0.009943368411839515</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6134677605296588</v>
+        <v>-0.6213125464210805</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7305938573530355</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.642207026214265</v>
+        <v>-1.650414178280158</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.607021841303947</v>
+        <v>-1.641175718616466</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.617416379238449</v>
+        <v>-1.627846014936601</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4584273792909386</v>
+        <v>-0.468667561592973</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.821299148585787</v>
+        <v>-0.8317082505128397</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1212319314074506</v>
+        <v>0.1103243900706019</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.582169162424762</v>
+        <v>0.5710783106622088</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.6816049384396479</v>
+        <v>0.670355684242864</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8279897067082373</v>
+        <v>0.8167280889775128</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.6993963403131502</v>
+        <v>0.7124625946136263</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.07480460232799402</v>
+        <v>-0.06162359303275622</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1358044885102956</v>
+        <v>-0.1226057495555324</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6789121296785794</v>
+        <v>-0.6655070020257483</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7959461557505421</v>
+        <v>-0.7824888620403243</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.551036682615639</v>
+        <v>-1.537584393895528</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.640140357862364</v>
+        <v>-1.650717703349279</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.673551539461471</v>
+        <v>-1.664122026795411</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.052106610912375</v>
+        <v>-1.060461485079813</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.221177652101936</v>
+        <v>-1.22973915161279</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1317376084827231</v>
+        <v>-0.1408133946245442</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1425676147879003</v>
+        <v>0.1333963325126675</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.276985844661624</v>
+        <v>0.2676637081557089</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.02731022117585979</v>
+        <v>0.01813354975745796</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3828913561452438</v>
+        <v>-0.3698251018447678</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.9721252024450493</v>
+        <v>-0.9589441931498115</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.114492053639559</v>
+        <v>-1.101293314684796</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.557782413606454</v>
+        <v>-1.544377285953622</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.721852255417936</v>
+        <v>-1.708394961707718</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.134987405639635</v>
+        <v>-2.121535116919524</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.963419048846184</v>
+        <v>-1.972117215147499</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.976441668238941</v>
+        <v>-1.968327596468299</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.032337750950006</v>
+        <v>-1.039337881824189</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8020506575478095</v>
+        <v>-0.8093696757803457</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.0372904384795163</v>
+        <v>-0.04496006871768543</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.03766732566342768</v>
+        <v>0.02998285437681147</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.09005085967253024</v>
+        <v>0.0822657295558642</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1999603966871391</v>
+        <v>-0.2075980957511163</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.5508538097768962</v>
+        <v>-0.5377875554764202</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.208151276999466</v>
+        <v>-1.194970267704228</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.383219604246413</v>
+        <v>-1.37002086529165</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.777071025015772</v>
+        <v>-1.763665897362941</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.057869976709782</v>
+        <v>-2.044412682999564</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.327669328870059</v>
+        <v>-2.314217040149948</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.23293103383935</v>
+        <v>-2.240071315516595</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.038601123665089</v>
+        <v>-2.031676613792214</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.177648846525763</v>
+        <v>-1.183368927797055</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7787935055684017</v>
+        <v>-0.7848475005540863</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3005923835430622</v>
+        <v>-0.3068663934474927</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2578439542975346</v>
+        <v>-0.2641216743733921</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1359689501557213</v>
+        <v>-0.1423569281845189</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2465170089587332</v>
+        <v>-0.252834543496121</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5450020621768701</v>
+        <v>-0.5319358078763941</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.261562019561858</v>
+        <v>-1.24838101026662</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.429437573717088</v>
+        <v>-1.416238834762325</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.673933973565099</v>
+        <v>-1.660528845912268</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.878687297882678</v>
+        <v>-1.86523000417246</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.16493114445602</v>
+        <v>-2.15147885573591</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.173895987762187</v>
+        <v>-2.17975225981526</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.94039911974189</v>
+        <v>-1.934604291184051</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.8708220605913723</v>
+        <v>-0.8755648599657917</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4905541018489288</v>
+        <v>-0.4955815481548882</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.09747019450801986</v>
+        <v>-0.1026700277641979</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1499356116509318</v>
+        <v>-0.1551083580691781</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2346818880646353</v>
+        <v>-0.2398809855095791</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1870142912222406</v>
+        <v>-0.1922037542221133</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7409169092988179</v>
+        <v>-0.7278506549983419</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.241612372423468</v>
+        <v>-1.22843136312823</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.470172580321595</v>
+        <v>-1.456973841366832</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.683568542829413</v>
+        <v>-1.670163415176582</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.888321867146992</v>
+        <v>-1.874864573436774</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.323107610605845</v>
+        <v>-2.309655321885735</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.222436672932538</v>
+        <v>-2.227125210051696</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.987993061287789</v>
+        <v>-1.983144976354403</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4477675304858977</v>
+        <v>-0.4517467217201485</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3296312225143296</v>
+        <v>-0.3337767192213974</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.07271466071654942</v>
+        <v>-0.07697503119586457</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.2108973484331571</v>
+        <v>-0.2151059972624765</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1605098209969995</v>
+        <v>-0.164779187701825</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.09980627626061533</v>
+        <v>-0.1040738914010788</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.612086609195984</v>
+        <v>-0.6162005499058623</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9521648284414255</v>
+        <v>-0.9389838191461877</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.299151368579878</v>
+        <v>-1.285952629625115</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.401048844638261</v>
+        <v>-1.405016643622595</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.764734146069628</v>
+        <v>-1.75127685235941</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.158168582317188</v>
+        <v>-2.161908235922716</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.052314462169079</v>
+        <v>-2.056123108754697</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.944301065213338</v>
+        <v>-1.940249228695272</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4278247114614899</v>
+        <v>-0.4311134189339896</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2611954640159198</v>
+        <v>-0.2646416132701077</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1229809437221903</v>
+        <v>-0.126496723181539</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2802386351657518</v>
+        <v>-0.283700036497379</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.285177676006775</v>
+        <v>-0.2886746159450695</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1840780349001108</v>
+        <v>-0.1875882191257148</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4652735510921673</v>
+        <v>-0.4687056439017354</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7802962681938155</v>
+        <v>-0.7671152588985777</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.098714045507819</v>
+        <v>-1.101986642445091</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.262443125255217</v>
+        <v>-1.265723296185804</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.633260657356367</v>
+        <v>-1.636443175351005</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.100204391650564</v>
+        <v>-2.103244279216511</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.985822058143441</v>
+        <v>-1.988926112855687</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.902357295473379</v>
+        <v>-1.898922924808211</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3271619736057616</v>
+        <v>-0.3299063729399663</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1957879214612035</v>
+        <v>-0.1986595006473664</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.04762522090732091</v>
+        <v>-0.05056311303842875</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3116140292846268</v>
+        <v>-0.3144691029019384</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4531835405238809</v>
+        <v>-0.4560278680510024</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3449955268241425</v>
+        <v>-0.3478569714611055</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.501792114695327</v>
+        <v>-0.5046137373772979</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.8223479474944284</v>
+        <v>-0.8091669381991906</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.043412317116719</v>
+        <v>-1.046102173900856</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.202756953004503</v>
+        <v>-1.205447716234268</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.655566957093491</v>
+        <v>-1.658137490654113</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.016185903289163</v>
+        <v>-2.018650207828649</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.833143059539367</v>
+        <v>-1.835685407400959</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.772954297565612</v>
+        <v>-1.770062816705725</v>
       </c>
     </row>
     <row r="30">
@@ -5156,101 +5156,101 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3544</v>
+        <v>3545</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4686914135733105</v>
+        <v>-0.4707951421452634</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3216082763528476</v>
+        <v>-0.3238231584688265</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3074214388704348</v>
+        <v>-0.309658318479805</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5840941550665093</v>
+        <v>-0.5862488149618201</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5724631366499011</v>
+        <v>-0.5746452074749655</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4286861987693342</v>
+        <v>-0.4308972215588014</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6390024736230941</v>
+        <v>-0.6411590686687703</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.7963267174750115</v>
+        <v>-0.7831457081797737</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.039246525555569</v>
+        <v>-1.041310963294109</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.282217179224652</v>
+        <v>-1.284250606599315</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.415137565343031</v>
+        <v>-1.417143424037192</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.788294378462702</v>
+        <v>-1.790194704560832</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.770056542366618</v>
+        <v>-1.771981098724353</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.730579505460717</v>
+        <v>-1.728226058764506</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 84.83</t>
+          <t>X &lt; 84.82</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3656</v>
+        <v>3657</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2993799936904864</v>
+        <v>-0.3010795182727719</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.260955226522114</v>
+        <v>-0.2627208207908822</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2866272991654313</v>
+        <v>-0.2884002259104719</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4961959741573239</v>
+        <v>-0.4979082502298198</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.5833556799435442</v>
+        <v>-0.5850633952200752</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5440128980569554</v>
+        <v>-0.5457221419771656</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6139864204380245</v>
+        <v>-0.6156803610287582</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.7933267405517697</v>
+        <v>-0.7949885369240235</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9487354775507768</v>
+        <v>-0.9503578167798494</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.100971376155421</v>
+        <v>-1.102582003103969</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.208711123649934</v>
+        <v>-1.210300193648031</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.514658832577744</v>
+        <v>-1.516164007729238</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.537120345271028</v>
+        <v>-1.538634597827141</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.545843445870986</v>
+        <v>-1.543932012105522</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3786</v>
+        <v>3787</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2428460590886345</v>
+        <v>-0.244073925271195</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1818945029477987</v>
+        <v>-0.1831787227032109</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3255324701632318</v>
+        <v>-0.3267892534822323</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3654125440442542</v>
+        <v>-0.3666562657393158</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3638525648573889</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3670643490954788</v>
+        <v>-0.3683148763677622</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4902258168461557</v>
+        <v>-0.4914466249296936</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5211736896031454</v>
+        <v>-0.5223985200682435</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6468949289347634</v>
+        <v>-0.6480887608813219</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8229893411769851</v>
+        <v>-0.8241583785546425</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.8548076801077542</v>
+        <v>-0.8559740261379005</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.17538133516571</v>
+        <v>-1.176462864815505</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.185002558784596</v>
+        <v>-1.186092571353512</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.211171540509646</v>
+        <v>-1.209772124419295</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3903</v>
+        <v>3904</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.01642095555215661</v>
+        <v>-0.01729591309753431</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1075662115905871</v>
+        <v>-0.1084453309526268</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1820472212731232</v>
+        <v>-0.1829143768078794</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3445827844441851</v>
+        <v>-0.3454066682906571</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.332384100558599</v>
+        <v>-0.3332205654455223</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3789524761588012</v>
+        <v>-0.3797724771825202</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5776934429685809</v>
+        <v>-0.5784644801687051</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5961386358000098</v>
+        <v>-0.5969132237591879</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.8222955370117973</v>
+        <v>-0.823013714979453</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.813858851486934</v>
+        <v>-0.8145938953080787</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.8764565715750479</v>
+        <v>-0.8771794533766126</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.03275153312218</v>
+        <v>-1.033434233548427</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.003413093963182</v>
+        <v>-1.004110789136739</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.021265202461755</v>
+        <v>-1.020268938368652</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01769808632095504</v>
+        <v>-0.01822946337017584</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1478193000234143</v>
+        <v>-0.1483350173528493</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2803137988447659</v>
+        <v>-0.2808008353815907</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3357629653306589</v>
+        <v>-0.3362351210506418</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3630654079004003</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3505170984211787</v>
+        <v>-0.3509885457597122</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3718917103642454</v>
+        <v>-0.3723589510292484</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4516565027670296</v>
+        <v>-0.45210890174436</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5738104982991672</v>
+        <v>-0.5742333229756298</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5125517149259906</v>
+        <v>-0.5129987680901209</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4789510613795471</v>
+        <v>-0.4794088427901997</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6302466836661722</v>
+        <v>-0.6306666255409894</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6373209171578367</v>
+        <v>-0.6377436514530856</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6981270554675376</v>
+        <v>-0.697505137724697</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03002368606362893</v>
+        <v>-0.03029423097326855</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.06744179411592199</v>
+        <v>-0.06771187969573589</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1318962571451578</v>
+        <v>-0.1321528447767335</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2568620690378651</v>
+        <v>-0.2570876034178582</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1473065347354918</v>
+        <v>-0.1475617889857617</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.153952327865376</v>
+        <v>-0.1542045132254657</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1765324900676362</v>
+        <v>-0.1767797419971302</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2883484791223552</v>
+        <v>-0.2885710300179909</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2137486156904203</v>
+        <v>-0.2139898413511077</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1948907219671696</v>
+        <v>-0.195141204834826</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1659328584486062</v>
+        <v>-0.1661916413547786</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1911944872519484</v>
+        <v>-0.1914470456348951</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2308099532233996</v>
+        <v>-0.2310551941783459</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3098301272361965</v>
+        <v>-0.3095221705395801</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/rsi/rsi_7.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_7.xlsx
@@ -568,261 +568,261 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 7.848</t>
+          <t>X ≈ 7.856</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>44</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.853847478098544</v>
+        <v>8.824826214645412</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.78168262823554</v>
+        <v>11.78059583315044</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.65723736221596</v>
+        <v>13.65718789508631</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.52379352368286</v>
+        <v>11.52337820718834</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.52478275232695</v>
+        <v>15.57331377268644</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.484458597863949</v>
+        <v>4.508391889695012</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.93864911176955</v>
+        <v>8.986617945947572</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.74377819089984</v>
+        <v>10.79299471465574</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.415640785627197</v>
+        <v>8.488833828761472</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.027719172493839</v>
+        <v>3.126974277005864</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.823909114005104</v>
+        <v>2.923747115179047</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.130582554615685</v>
+        <v>5.254223451413075</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.983958564061417</v>
+        <v>7.132615109230315</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>9.484108855968152</v>
+        <v>9.656107615534815</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 10.99</t>
+          <t>X ≈ 11</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.473613491467162</v>
+        <v>-2.502729866612697</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.454438342437079</v>
+        <v>-6.455670366403282</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.224402819578145</v>
+        <v>-9.224619775032274</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.34625773104257</v>
+        <v>-4.346778100252301</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.884612869846492</v>
+        <v>-4.836205650958028</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.916304803463831</v>
+        <v>4.940240463468513</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.456149523130527</v>
+        <v>2.504087322334158</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.141839379783192</v>
+        <v>-5.092687766713667</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.307995222987913</v>
+        <v>4.38117345681686</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.838699102263135</v>
+        <v>5.93796009941417</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.256441150123877</v>
+        <v>3.356278660602634</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.051147481109105</v>
+        <v>8.174791329506341</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.252753157217271</v>
+        <v>5.401407909214399</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.479779851640231</v>
+        <v>5.651778611205813</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 14.13</t>
+          <t>X ≈ 14.14</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>73</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.401344998470883</v>
+        <v>7.025279326682607</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.528188630512091</v>
+        <v>8.15859385453782</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.60040028870238</v>
+        <v>13.22907806713287</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.634706178754037</v>
+        <v>9.262285062950099</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.265983979878214</v>
+        <v>1.935482650740525</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.930494282706384</v>
+        <v>2.954418854101867</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.622993739282172</v>
+        <v>-2.575082950246966</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.457732951769607</v>
+        <v>-4.4085818349755</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4154434273078778</v>
+        <v>-0.3422838054716379</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.472458596414249</v>
+        <v>1.571705153708237</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.838128243236163</v>
+        <v>-2.738305573993649</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.435334378586838</v>
+        <v>-1.311705218041723</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.59474565261975</v>
+        <v>-4.446098806189411</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.109264522220329</v>
+        <v>1.281263281786373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 17.27</t>
+          <t>X ≈ 17.28</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>97</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.341960248052139</v>
+        <v>8.741537702557046</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.793739633139609</v>
+        <v>9.172737577535052</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.43019823614662</v>
+        <v>10.83329626014904</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.506947629446294</v>
+        <v>9.934921482752927</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.915269603426609</v>
+        <v>7.37376632866593</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.213860810225668</v>
+        <v>7.651048545335811</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.073065510121602</v>
+        <v>5.05860011498509</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.666521912858379</v>
+        <v>6.179549564467848</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.629739152510403</v>
+        <v>-2.556592142560241</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3898094765997797</v>
+        <v>-0.2905727347622857</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5943435108893524</v>
+        <v>-0.4945198648564428</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.5601770132212707</v>
+        <v>-0.4365496189452927</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9803280609326137</v>
+        <v>-0.831680553326585</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.785806795391267</v>
+        <v>-1.613808035824604</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 20.41</t>
+          <t>X ≈ 20.42</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>98</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.610055643685207</v>
+        <v>2.584365058871342</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.039123763172917</v>
+        <v>3.041842593514076</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.698127629925487</v>
+        <v>5.70489844708549</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.759667290156052</v>
+        <v>1.761559527413453</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8123835031594595</v>
+        <v>-0.7643803160828924</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.539153171660843</v>
+        <v>2.56534015967047</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4186763675391632</v>
+        <v>0.4669006826625264</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.04746159681215545</v>
+        <v>0.001726272936664941</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.929863458138669</v>
+        <v>2.003022152068361</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.06206964055311914</v>
+        <v>0.1613020000724958</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1423347527705019</v>
+        <v>-0.04251450791998934</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1080583150321672</v>
+        <v>0.01556614352177377</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.552451522749379</v>
+        <v>3.701100362625546</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.738283252999693</v>
+        <v>1.910282012567286</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>125</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.670047538207285</v>
+        <v>-4.117356489747245</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.47945265181685</v>
+        <v>-4.912475413610672</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.077337995072106</v>
+        <v>-3.710627593173371</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.149557937461807</v>
+        <v>-3.582827667630333</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.292761251100558</v>
+        <v>-1.680044978227457</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.382091137731855</v>
+        <v>-6.99942546382286</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.065037244465906</v>
+        <v>-8.660335857684608</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-11.13108562986732</v>
+        <v>-10.72789223837694</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.803829550882902</v>
+        <v>-4.372479858551081</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-8.850509540933274</v>
+        <v>-8.751314213738929</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-10.65603420020349</v>
+        <v>-10.55624592396622</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.825118710073667</v>
+        <v>-9.701515059541435</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-13.44697619993989</v>
+        <v>-13.29834400487685</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-10.82498205312275</v>
+        <v>-10.65298329355682</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>144</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.16554103319352</v>
+        <v>-3.227455841468306</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.003711292050056</v>
+        <v>-2.057337807113825</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.70634689810089</v>
+        <v>-2.452055614617912</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.041134817917772</v>
+        <v>6.000816612868384</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.813768836221776</v>
+        <v>4.117448903536733</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4302736399249412</v>
+        <v>-0.4673470212834872</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.723092580940929</v>
+        <v>5.71362979688066</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.792397862877607</v>
+        <v>2.463906251955208</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.731688399742623</v>
+        <v>2.428769440148741</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.883453712903524</v>
+        <v>1.59135595908888</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.373131603079798</v>
+        <v>1.774578673015995</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.101753383855055</v>
+        <v>2.22537027894375</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.765013547440276</v>
+        <v>3.913656101498496</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.297240169099467</v>
+        <v>3.469238928666606</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.552071164895487</v>
+        <v>2.506401478360232</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8561530285402483</v>
+        <v>-1.240798251686137</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9160536625129154</v>
+        <v>0.5212869131167253</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.156283437778498</v>
+        <v>1.371408416498973</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.95687398697433</v>
+        <v>5.193401439491041</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.97949814223373</v>
+        <v>6.184405020689397</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11.23589818394107</v>
+        <v>10.43820984248025</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>8.603556768309154</v>
+        <v>7.809795915359445</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.927163101198637</v>
+        <v>4.1777695045256</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.080030303755258</v>
+        <v>3.346608467582008</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.152858915563058</v>
+        <v>3.139693577186499</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2911617325825446</v>
+        <v>0.3222136221736065</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.768856864912294</v>
+        <v>2.490138461347378</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.801793647325646</v>
+        <v>-3.015573221613813</v>
       </c>
     </row>
     <row r="14">
@@ -991,98 +991,98 @@
         <v>158</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.9830810572782127</v>
+        <v>0.9565246536231129</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.890174752754696</v>
+        <v>1.893973174439353</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.106434981721691</v>
+        <v>-5.456433752558794</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.07068266530788492</v>
+        <v>-0.2653109966221407</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4657294544061159</v>
+        <v>-0.7576858070156121</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.430518121475934</v>
+        <v>-1.751481504872949</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.147151748349053</v>
+        <v>-2.444669770570115</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.349667239470861</v>
+        <v>-1.649988769207319</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1471619777824884</v>
+        <v>-0.421138593533982</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.259861139698529</v>
+        <v>-2.517805453922186</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6966873644081417</v>
+        <v>0.4399565490348394</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.628705853977102</v>
+        <v>2.397236679548278</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.852257665191608</v>
+        <v>-3.063866897788117</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.7287795214771862</v>
+        <v>-1.189692154315722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 36.12</t>
+          <t>X ≈ 36.13</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>160</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.58946952069288</v>
+        <v>-5.628461844617497</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2800240514986854</v>
+        <v>0.2808933126355342</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.359564940648362</v>
+        <v>-1.361546269258</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6077645523660209</v>
+        <v>-0.6072495879519408</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.217749628979384</v>
+        <v>3.278608001905354</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.750461176226906</v>
+        <v>9.801393520724147</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8.421982583415215</v>
+        <v>8.490737431498687</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.583291182447383</v>
+        <v>8.649904671115337</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.533417397138635</v>
+        <v>3.612932061978547</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.438062685332852</v>
+        <v>1.539103481163558</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.6390477402418213</v>
+        <v>-0.5400369663725257</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-6.22632507115339</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-7.273151991788566</v>
+        <v>-7.127028155571601</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.424982053122612</v>
+        <v>-6.25298329355595</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>159</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.533464037503173</v>
+        <v>-1.56500704320208</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.513169890694464</v>
+        <v>-2.518933975193939</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.360766111958867</v>
+        <v>3.371832504411159</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.862638064181233</v>
+        <v>2.874225610952536</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.07298719954052</v>
+        <v>1.128450769200818</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.625147160386973</v>
+        <v>2.659097923239727</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5951415589419682</v>
+        <v>-0.5462122540359076</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4326904366233677</v>
+        <v>-0.3831141968091885</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1345917917231105</v>
+        <v>0.208844011664084</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.170952429575465</v>
+        <v>1.271807883679287</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9670664461569913</v>
+        <v>1.067667436143196</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.630271529415687</v>
+        <v>1.754764991118151</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.611765107708884</v>
+        <v>5.762122787824907</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.46809970788339</v>
+        <v>6.640098467450336</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>184</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.389920362135541</v>
+        <v>-1.162566441135503</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.161669295232159</v>
+        <v>-4.924830183477667</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.848942728533061</v>
+        <v>-2.604124553202858</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.51054746494971</v>
+        <v>-6.276698196565057</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.091092152675095</v>
+        <v>-1.042044172007827</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2523821252036882</v>
+        <v>-0.2257803923192085</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.290001199833739</v>
+        <v>1.343998301063905</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.2588008569691667</v>
+        <v>-0.20879098105857</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.8617534845103023</v>
+        <v>-0.7892418510649364</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4608585331151502</v>
+        <v>0.5608426115983463</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.914658271899199</v>
+        <v>-1.81721087941601</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.139431141592887</v>
+        <v>-5.019913707268501</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.474903962622214</v>
+        <v>-4.328115112093201</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.968460313992324</v>
+        <v>-6.796461554425782</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.05350646386974489</v>
+        <v>-0.08308694451325493</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.152720314428102</v>
+        <v>-2.149940132638065</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.575300411939345</v>
+        <v>-1.574049838464767</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.846994658906951</v>
+        <v>-4.84257975034663</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.790644543247609</v>
+        <v>-8.729887143725847</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.63162251777981</v>
+        <v>-3.602732692868088</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-6.8611428241543</v>
+        <v>-7.061447034520732</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.841493948591086</v>
+        <v>-7.041842901700186</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.825396694586431</v>
+        <v>-9.991436870060284</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-10.67702456762814</v>
+        <v>-10.81526545087527</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-8.449251588301969</v>
+        <v>-8.592221432391945</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-8.418184458004951</v>
+        <v>-8.534054695026938</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.428616845065285</v>
+        <v>-5.531154369163694</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.205469858000804</v>
+        <v>-5.282109507148213</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.009688246690708</v>
+        <v>-3.001489303431441</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.139897706701795</v>
+        <v>-3.100462445068885</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.026245173352997</v>
+        <v>-1.021504301334311</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.108211009113184</v>
+        <v>1.08840169731247</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.338324868520068</v>
+        <v>1.094202061311165</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.410467056547674</v>
+        <v>1.862037085080701</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3200652349874318</v>
+        <v>-0.1788170239468556</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.357547401355255</v>
+        <v>1.830597740422157</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.305749489837517</v>
+        <v>4.763922160988557</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.456536354701889</v>
+        <v>4.930192590074569</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>5.251906411993588</v>
+        <v>4.726052142538364</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.774858573098093</v>
+        <v>2.308971355150554</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.3436366843486098</v>
+        <v>-0.06638459121502649</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.363962670495219</v>
+        <v>0.6777097757507207</v>
       </c>
     </row>
     <row r="20">
@@ -1303,202 +1303,202 @@
         <v>185</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.28227908345773</v>
+        <v>-3.316115250645133</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.888130989718341</v>
+        <v>-4.899138527289075</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.28417241895027</v>
+        <v>-5.295577052996798</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.8424600114021459</v>
+        <v>-0.8436293436292317</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8407499942534997</v>
+        <v>-0.7923379440408453</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.240579717991324</v>
+        <v>-3.222255127924747</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.245544945663958</v>
+        <v>-2.201830136068885</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.171909786075453</v>
+        <v>-2.12712235591156</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.312229867490117</v>
+        <v>-3.245176046129679</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.082102623440122</v>
+        <v>-2.98792354586358</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5879307388045021</v>
+        <v>-0.4893612906969764</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.715033370410879</v>
+        <v>-2.593356715494004</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.515582568213901</v>
+        <v>-1.366893020436322</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.370927999068449</v>
+        <v>-2.198929239502036</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 54.98</t>
+          <t>X ≈ 54.97</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>184</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.472194255903368</v>
+        <v>-2.505650658208765</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.535248551444575</v>
+        <v>-3.545311263982413</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6809701067720724</v>
+        <v>-0.6824084037357139</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.01065236662510927</v>
+        <v>-0.009316770186465817</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.089641248427483</v>
+        <v>-1.042044172007699</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.50304464810597</v>
+        <v>-3.486649957536592</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.206392958836858</v>
+        <v>0.257041779324652</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.05209068881144</v>
+        <v>-4.013138807145523</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.402599874417845</v>
+        <v>-1.332720111934499</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.165800737361543</v>
+        <v>-1.069592171010228</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.371213580324486</v>
+        <v>-1.273732618546319</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2511938178759294</v>
+        <v>-0.1286093594422866</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.759413355523321</v>
+        <v>-1.610723807745373</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.077155966166238</v>
+        <v>-1.905157206599576</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 58.12</t>
+          <t>X ≈ 58.11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.628590144529483</v>
+        <v>-8.426603560305686</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.313375186526407</v>
+        <v>-6.062324044101807</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.352049195252832</v>
+        <v>-3.072881912354568</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-5.463383641126484</v>
+        <v>-5.204600484261505</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.880526222540389</v>
+        <v>-4.563906122388566</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.18301222010079</v>
+        <v>-9.940838117693929</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-14.18567856056455</v>
+        <v>-13.95629646680626</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-12.4158606290646</v>
+        <v>-12.16224222154003</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-13.60474130142729</v>
+        <v>-13.32915833350168</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-12.77770322781166</v>
+        <v>-12.45807166007943</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-13.55117237736732</v>
+        <v>-13.22718385902783</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-9.594558424431696</v>
+        <v>-9.214214861776121</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.088919950540294</v>
+        <v>-5.654570528452815</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.863184300313897</v>
+        <v>-5.405525666437448</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.26</t>
+          <t>X ≈ 61.25</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>172</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7280686877116267</v>
+        <v>-0.7615121284189144</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.197260955718654</v>
+        <v>5.204748207920559</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.322678015856468</v>
+        <v>0.7451698778218017</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.444614072574147</v>
+        <v>-1.450166112956808</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.560696534751251</v>
+        <v>-3.102205951583151</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.421159030282119</v>
+        <v>-3.410815781601428</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.924025207860879</v>
+        <v>-2.890076521989613</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.548229676928294</v>
+        <v>-4.518699980047444</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.19219992958358</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.883218742021178</v>
+        <v>-4.798105821162082</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.834014905277499</v>
+        <v>-6.746432315209802</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.062377160262322</v>
+        <v>-4.944079531333209</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.069322354512146</v>
+        <v>-6.502028155571395</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.936609960099503</v>
+        <v>-3.346006549370038</v>
       </c>
     </row>
     <row r="24">
@@ -1511,566 +1511,566 @@
         <v>177</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.306175441185701</v>
+        <v>-3.092190483056761</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4114245228677191</v>
+        <v>-0.1689325479152828</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.185719246821385</v>
+        <v>-3.383128192583612</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.618842100649417</v>
+        <v>-4.639628732849076</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.467652306795387</v>
+        <v>-2.868990868151279</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9191448686919159</v>
+        <v>-1.466261846507493</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4382486493447146</v>
+        <v>-0.3969744329081593</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.026473107333722</v>
+        <v>-2.557722447528718</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.089310561248318</v>
+        <v>-2.594695056665515</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1206288628147973</v>
+        <v>-0.5936648804183591</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.801496997146252</v>
+        <v>0.3321381748704155</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2694834089822749</v>
+        <v>-0.174666839177128</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.283486064931139</v>
+        <v>-1.134796517153447</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.4927786632922491</v>
+        <v>0.2441918476868494</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 67.55</t>
+          <t>X ≈ 67.54</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>177</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.008156383258985</v>
+        <v>3.675774908724918</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.088132941645711</v>
+        <v>4.348392353783382</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.127566920679769</v>
+        <v>2.575119994297822</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.570654932170633</v>
+        <v>1.575060532687644</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.77684616151911</v>
+        <v>-1.739047365326421</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.7690681607666292</v>
+        <v>1.358596910554652</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.809063220752748</v>
+        <v>-3.78680494138267</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.8966584269527758</v>
+        <v>-0.8628071932914381</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.08525429281601</v>
+        <v>-2.029723305253093</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.809077297296604</v>
+        <v>-1.158636631830845</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.017341453156618</v>
+        <v>-1.927748830779308</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.810134170994225</v>
+        <v>-4.694440850476553</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.978401319168491</v>
+        <v>-2.829711771390663</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.752665668941958</v>
+        <v>-3.145638660787732</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 70.69</t>
+          <t>X ≈ 70.68</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.355280159867583</v>
+        <v>8.131838579579544</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.634428066613097</v>
+        <v>2.614028163127891</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3935259406364722</v>
+        <v>1.000777979691307</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.335492229591985</v>
+        <v>-1.91811846689896</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.210970329572014</v>
+        <v>0.6414128799540038</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.513589388245308</v>
+        <v>0.9141983987729319</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.405276398307642</v>
+        <v>1.463298407108446</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.369812084601847</v>
+        <v>4.656002232090948</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.822687127636478</v>
+        <v>2.180005232710329</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.436819334445218</v>
+        <v>3.185444944578272</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.501613267807187</v>
+        <v>0.5422801067982022</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5250049438991553</v>
+        <v>0.6004468441630948</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.113257451930217</v>
+        <v>0.8150450151602442</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.145478947532688</v>
+        <v>-1.374934513068283</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 73.83</t>
+          <t>X ≈ 73.82</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.01939184536446703</v>
+        <v>-0.3672546820299232</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.305056039783238</v>
+        <v>0.9067110899571702</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.269207644836094</v>
+        <v>-1.629884041214808</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.87331374510979</v>
+        <v>-1.5</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.145934542067472</v>
+        <v>-2.703534855237599</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.114229268570398</v>
+        <v>-1.716463622132991</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.881319864797348</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.12377539805491</v>
+        <v>2.757047528258205</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.044936804654384</v>
+        <v>2.720074919121409</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.890569432170118</v>
+        <v>1.181960624020626</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.9467196426116686</v>
+        <v>0.2635344621989049</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7561142952914324</v>
+        <v>-1.821155943293348</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4463381413054961</v>
+        <v>-1.502028155571452</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9505294983782306</v>
+        <v>-1.967269007841807</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 76.97</t>
+          <t>X ≈ 76.96</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>124</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.356748288502253</v>
+        <v>2.328597852532369</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.552569449283709</v>
+        <v>1.55187238027974</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.962761689824184</v>
+        <v>1.964586004868316</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.12788948204394</v>
+        <v>-1.131336405529964</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.887055350596036</v>
+        <v>-4.846391998094823</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.590411188300301</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.451909656624139</v>
+        <v>-1.408456116888416</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.916934671860879</v>
+        <v>-1.874288877271759</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4348362425214276</v>
+        <v>0.5080933523010316</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3913690590948491</v>
+        <v>0.4907163843894651</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.232686937874973</v>
+        <v>-2.132778901856398</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2210460531899372</v>
+        <v>0.3447426742181818</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.220250038586201</v>
+        <v>2.368939586364029</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.639534075909509</v>
+        <v>1.811532835476214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 80.11</t>
+          <t>X ≈ 80.1</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.900992520525264</v>
+        <v>-4.684024868365242</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.370660282530508</v>
+        <v>-2.644013547724001</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.618854286333217</v>
+        <v>-5.936302260676385</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.199911416402713</v>
+        <v>-6.531055900621119</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.457445026595764</v>
+        <v>-2.672478954616565</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.44795937086112</v>
+        <v>-2.399693435797595</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.957514996657572</v>
+        <v>-3.909624887341892</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1427910069895688</v>
+        <v>0.6970061203907107</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.9246107620868642</v>
+        <v>-0.7892418510649364</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.203100986988197</v>
+        <v>-3.062345794198706</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.704528251018786</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.313419626064871</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2221462747779057</v>
+        <v>-0.7049267062960922</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7106963388370389</v>
+        <v>-1.180519525440197</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 83.25</t>
+          <t>X ≈ 83.24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.062873778382915</v>
+        <v>6.26181799967447</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.65602117030538</v>
+        <v>0.2926760022378687</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3683926426932018</v>
+        <v>-0.9782549685329798</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.270114601568174</v>
+        <v>0.9060150375939315</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9510116212272024</v>
+        <v>-2.214813050726306</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.216535680764167</v>
+        <v>-3.696413496819765</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1502439508704327</v>
+        <v>0.628895326235579</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.221055812115488</v>
+        <v>-1.591323399060038</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>1.880475921627671</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.565419270637207</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.34219785475166</v>
+        <v>5.238471805557303</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.162290292821218</v>
+        <v>7.928217490290571</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.84928229665077</v>
+        <v>6.655866581270644</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.289303661162954</v>
+        <v>5.150525478373737</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 86.39</t>
+          <t>X ≈ 86.38</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.365237815619444</v>
+        <v>0.925002678929765</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.061744030247972</v>
+        <v>2.395260708277782</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.40995043143014</v>
+        <v>-1.05191239454075</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.335659327542828</v>
+        <v>3.658124318429699</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.874292851370178</v>
+        <v>6.222310291981557</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.633205342543768</v>
+        <v>4.205019474922665</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.010033444816116</v>
+        <v>2.617645828445227</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.158349416413955</v>
+        <v>6.731965739817618</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.866598029121924</v>
+        <v>7.458351909306799</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.016679232792065</v>
+        <v>6.634523328491817</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.1196703822242</v>
+        <v>8.720459216833603</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.384817765348735</v>
+        <v>8.015267175572468</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>8.7338976812661</v>
+        <v>8.383468027634642</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.190402562261859</v>
+        <v>7.869154111024052</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 89.54</t>
+          <t>X ≈ 89.53</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>117</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.348143798525477</v>
+        <v>7.318948004172846</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.318154286658228</v>
+        <v>2.316967500213572</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.487485466005758</v>
+        <v>4.487332076001437</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3442063360898686</v>
+        <v>0.3437118437118656</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.6606176376949833</v>
+        <v>0.7091635574607551</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.7514100420716474</v>
+        <v>-0.7274526331220343</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.400222965440378</v>
+        <v>-3.352211286450057</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.012590754526265</v>
+        <v>-2.963343192132548</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.492376329852434</v>
+        <v>-6.419119220072737</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.564090301536496</v>
+        <v>-1.46418226551782</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.598492979023973</v>
+        <v>3.722189600052218</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.887743835112232</v>
+        <v>5.03643338289006</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.113479485338765</v>
+        <v>5.285478244905427</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 92.68</t>
+          <t>X ≈ 92.67</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>103</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.05373156451492633</v>
+        <v>-0.08292735886755764</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.664917657578762</v>
+        <v>-1.666104444023418</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.001436615149323</v>
+        <v>-4.001590005153645</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.01228367407008335</v>
+        <v>0.01178918169208032</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.496879665433362</v>
+        <v>-1.44833374566759</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7422419370172619</v>
+        <v>0.766199345966875</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.453648082605447</v>
+        <v>7.501659761595768</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.044831866003165</v>
+        <v>5.094079428396881</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.867344855111483</v>
+        <v>8.940601964891179</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.93004741800492</v>
+        <v>11.02939474329949</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>14.60884140537578</v>
+        <v>14.70874944139446</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>14.64321955773114</v>
+        <v>14.76691617875938</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>13.25219491800996</v>
+        <v>13.40088446578779</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.53618299542097</v>
+        <v>11.70818175498763</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 95.82</t>
+          <t>X ≈ 95.81</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>81</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.629064178682512</v>
+        <v>-0.6582599730351433</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.932589234426516</v>
+        <v>3.93140244798186</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.241521553375172</v>
+        <v>7.241368163370851</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.66804299325981</v>
+        <v>3.667548500881807</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.53716084757156</v>
+        <v>10.58570676733734</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9.599966975972066</v>
+        <v>9.623924384921679</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.515256616705898</v>
+        <v>9.563268295696219</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.813620071684603</v>
+        <v>7.86286763407832</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>17.62918112503837</v>
+        <v>17.70243823481807</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.54469442747394</v>
+        <v>15.64404175276852</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.33999326921372</v>
+        <v>15.4399013052324</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.54721092774191</v>
+        <v>21.67090754877015</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19.89249217319392</v>
+        <v>20.04118172097174</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.88365992218586</v>
+        <v>19.05565868175253</v>
       </c>
     </row>
   </sheetData>
@@ -2210,261 +2210,261 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 6.277</t>
+          <t>X &gt; 6.285</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088</v>
+        <v>4099</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1278314170254475</v>
+        <v>-0.126843342396711</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1164923675006193</v>
+        <v>-0.1161543928937192</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2053414273578582</v>
+        <v>-0.2047884555351587</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.06187042430610035</v>
+        <v>-0.06169384278413759</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.123153685495403</v>
+        <v>-0.123899300918545</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.007720138225465689</v>
+        <v>-0.008230292278049944</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.01858045336307157</v>
+        <v>0.0174666083131072</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01988514823977994</v>
+        <v>-0.02092358710633135</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.005897771646687033</v>
+        <v>0.004257598040929622</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.04923807180251316</v>
+        <v>0.04690265250161474</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.05380346986497386</v>
+        <v>0.05144279959529285</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1019514873724319</v>
+        <v>0.09893323356246952</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1602385206663683</v>
+        <v>0.1565084297943926</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1552527805367419</v>
+        <v>0.1510176822916733</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 9.419</t>
+          <t>X &gt; 9.426</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4044</v>
+        <v>4055</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2255549262701209</v>
+        <v>-0.2239761316716411</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-0.2452436678495715</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3561706723482914</v>
+        <v>-0.355202009031423</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1879261151348643</v>
+        <v>-0.1874011597258871</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2934081867971372</v>
+        <v>-0.2942266437640768</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05659646473089452</v>
+        <v>-0.05723926293324411</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.07847271700534009</v>
+        <v>-0.07985587229254776</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1369972122660315</v>
+        <v>-0.138263267815951</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.08560289418296918</v>
+        <v>-0.08780685427761625</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.01683125468322544</v>
+        <v>0.01348140676100229</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.02366384366760599</v>
+        <v>0.02027599567774274</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.04723838970707561</v>
+        <v>0.04299420283856392</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.08599428676195942</v>
+        <v>0.0808120811149351</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.05375187368239409</v>
+        <v>0.04787983837979226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 12.56</t>
+          <t>X &gt; 12.57</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4002</v>
+        <v>4013</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2019621077448122</v>
+        <v>-0.2001267280166488</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1807917100456109</v>
+        <v>-0.1802454317819695</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2631007697536702</v>
+        <v>-0.2623748108823989</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1442854534986608</v>
+        <v>-0.1438691807819339</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2452246294038076</v>
+        <v>-0.2466903571201371</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1087858333626244</v>
+        <v>-0.1095428135210597</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1050729504100687</v>
+        <v>-0.106899384421709</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.08447263179733966</v>
+        <v>-0.08641033261692854</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1317126195505836</v>
+        <v>-0.1345791376232413</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.04426780818492659</v>
+        <v>-0.04852410160965093</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.01026335445112636</v>
+        <v>-0.01463855999802632</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.03676065622968139</v>
+        <v>-0.04211306836005946</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.03177043055028861</v>
+        <v>0.02512680207676965</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.003192947675479729</v>
+        <v>-0.01077048518330059</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 15.7</t>
+          <t>X &gt; 15.71</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3929</v>
+        <v>3940</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3246501756383608</v>
+        <v>-0.333998464563102</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3240229558742556</v>
+        <v>-0.3347467688127637</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.502101934749156</v>
+        <v>-0.5123433540537476</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3073972858108078</v>
+        <v>-0.3181456426581875</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.273302569968223</v>
+        <v>-0.2871214813774543</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1652550236077346</v>
+        <v>-0.1663116464491026</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.0582905076542346</v>
+        <v>-0.06116907977570207</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.003218367771381736</v>
+        <v>-0.006329490060529963</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1264409603583445</v>
+        <v>-0.1307308024067524</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.07244826823475137</v>
+        <v>-0.07854357765996411</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.04227778499435431</v>
+        <v>0.03582532122575088</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01077544835691668</v>
+        <v>-0.01859016812483105</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1177301338008405</v>
+        <v>0.1079693070014898</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.02386217529124934</v>
+        <v>-0.03470918188096306</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 18.84</t>
+          <t>X &gt; 18.85</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3832</v>
+        <v>3843</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5693425584927354</v>
+        <v>-0.5630713264446214</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5801354222454265</v>
+        <v>-0.5747223039664888</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7788329150667224</v>
+        <v>-0.7987152100458559</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5305161419642346</v>
+        <v>-0.5769402071038954</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4299548405369364</v>
+        <v>-0.4804876321904175</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.32673055489213</v>
+        <v>-0.3636272692966429</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1628681521543029</v>
+        <v>-0.1903956246343625</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1467373675681074</v>
+        <v>-0.1624653912547203</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.06307459171566165</v>
+        <v>-0.06950037045388768</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.06441485560129223</v>
+        <v>-0.07319181387153151</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.05839267687868244</v>
+        <v>0.04921160357027077</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.003131637183741987</v>
+        <v>-0.008040580112968598</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1455254482291082</v>
+        <v>0.1316867247615292</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.02073819739916871</v>
+        <v>0.005148374411646728</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3734</v>
+        <v>3745</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.652786860531684</v>
+        <v>-0.6454341477426055</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6751240136142016</v>
+        <v>-0.6693613853958809</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9488227740408064</v>
+        <v>-0.9689032309801391</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.590622723739223</v>
+        <v>-0.6381345926800535</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4199178804573975</v>
+        <v>-0.473058664761453</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4019465712826502</v>
+        <v>-0.4402731459425198</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1781309702930187</v>
+        <v>-0.2075959018346438</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1493428912783656</v>
+        <v>-0.1667619955513189</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1153798752951332</v>
+        <v>-0.1237346046881171</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.0677344808351279</v>
+        <v>-0.07932810059156736</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.06366083116513011</v>
+        <v>0.0516119130298307</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.006049852319577553</v>
+        <v>-0.00865832615200901</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.05610960588766289</v>
+        <v>0.03828150806975827</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.02433931075531603</v>
+        <v>-0.04470558995129181</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3609</v>
+        <v>3620</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.5482821266138629</v>
+        <v>-0.5255473265407886</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5433586825597985</v>
+        <v>-0.5228450170183052</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8404646685742208</v>
+        <v>-0.8742304284182154</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.501992382449302</v>
+        <v>-0.5364532019704455</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3896863976836613</v>
+        <v>-0.4313809605671892</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1601848448193266</v>
+        <v>-0.2137830797173592</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1296726551632261</v>
+        <v>0.08428047785630355</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2310167214463874</v>
+        <v>0.1979179161484623</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.04700754766094661</v>
+        <v>0.02297621208892764</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2364624940920734</v>
+        <v>0.2201189337021958</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4349442556375891</v>
+        <v>0.417905346627748</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3465585999779677</v>
+        <v>0.3260397654705542</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5237975321077784</v>
+        <v>0.4988003448427847</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3497477889387568</v>
+        <v>0.3216023418030289</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3465</v>
+        <v>3476</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4395129253014574</v>
+        <v>-0.4136155583734791</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.4826687039835775</v>
+        <v>-0.4592756954493282</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.8044799525419393</v>
+        <v>-0.8088659788173089</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.77391455181521</v>
+        <v>-0.8072722046565204</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6059338879238823</v>
+        <v>-0.6198250055703411</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1489603754123365</v>
+        <v>-0.2032787046927567</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1027811599340254</v>
+        <v>-0.1489261682712879</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1661281545297584</v>
+        <v>0.10404498163863</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.02300516307492018</v>
+        <v>-0.07668840955682299</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.209574547336274</v>
+        <v>0.1633127968622432</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3959546515880348</v>
+        <v>0.3617025390903805</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2736154401285305</v>
+        <v>0.2473563379848969</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3890976457563085</v>
+        <v>0.3573333629790199</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2272545991138983</v>
+        <v>0.1912054291136371</v>
       </c>
     </row>
     <row r="14">
@@ -2630,101 +2630,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3327</v>
+        <v>3337</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5636002725954654</v>
+        <v>-0.5352464747972121</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4671770187449766</v>
+        <v>-0.4267220139039551</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.8758456390094977</v>
+        <v>-0.8642724073395769</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8954556767217028</v>
+        <v>-0.8980233602875174</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8781513471171465</v>
+        <v>-0.8619701886280353</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4446403499945859</v>
+        <v>-0.4693524349379246</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5730960831245113</v>
+        <v>-0.5899246415989694</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1838463416234006</v>
+        <v>-0.2169317578840548</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2283322506822998</v>
+        <v>-0.2539043670208514</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.04903264941447105</v>
+        <v>0.03071522472258437</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2816015441553503</v>
+        <v>0.2459875992356189</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2728876408022103</v>
+        <v>0.2442382191649273</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.290388065881487</v>
+        <v>0.2684931146502265</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3528959150167097</v>
+        <v>0.3247811655389015</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 34.55</t>
+          <t>X &gt; 34.56</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3169</v>
+        <v>3179</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.6407147093641754</v>
+        <v>-0.6093892361342412</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5847098618806541</v>
+        <v>-0.542063265793935</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6649169182305457</v>
+        <v>-0.6360366437206295</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9436254015688803</v>
+        <v>-0.9294699011680123</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.8987138775836456</v>
+        <v>-0.8671532437695149</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3954864566862781</v>
+        <v>-0.4056291279074955</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4946168167611589</v>
+        <v>-0.4977416499734701</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.1257208440342836</v>
+        <v>-0.1457071565034056</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2323792380973089</v>
+        <v>-0.2455926313212302</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1641494744948986</v>
+        <v>0.1573796686439053</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2609061955911471</v>
+        <v>0.2363471166724551</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1554312578165309</v>
+        <v>0.1372316898347705</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4470740947579657</v>
+        <v>0.4341152857622959</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4068260882467669</v>
+        <v>0.4000522522130225</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3009</v>
+        <v>3019</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3775705518990407</v>
+        <v>-0.3433900253500966</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6306910603321967</v>
+        <v>-0.5856780563035997</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6279798349514323</v>
+        <v>-0.597586315769</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.9614844031881731</v>
+        <v>-0.9465468306527995</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.117601933765123</v>
+        <v>-1.086868977226942</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9349851676421039</v>
+        <v>-0.9465776617866197</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.9687463960327491</v>
+        <v>-0.9741102001674307</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5888122113447096</v>
+        <v>-0.61185418943451</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4326210000241062</v>
+        <v>-0.4500854935034013</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.09641065304788299</v>
+        <v>0.08415151031228874</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3087601768916741</v>
+        <v>0.2774936729120014</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4947735684297498</v>
+        <v>0.4681546136554999</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8575879444912431</v>
+        <v>0.8348383565186452</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7700993692767071</v>
+        <v>0.7526477100874942</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2850</v>
+        <v>2860</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3130838627021788</v>
+        <v>-0.2754749533786054</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5256685571646145</v>
+        <v>-0.4781998426310352</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.8505098719895798</v>
+        <v>-0.8182637956321699</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.174830182946671</v>
+        <v>-1.158960403455339</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.239813748570597</v>
+        <v>-1.21002836173114</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.133603076468994</v>
+        <v>-1.147033052702419</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.9895896132599233</v>
+        <v>-0.997898932137673</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.5975221629870617</v>
+        <v>-0.6245708533601828</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4642655031426486</v>
+        <v>-0.486718287671799</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.0364625328837036</v>
+        <v>0.01812446018454494</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2720336166063433</v>
+        <v>0.2335644322288744</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4314247348168578</v>
+        <v>0.3966262744888738</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5923549027538328</v>
+        <v>0.5609089073656008</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.4522109293333827</v>
+        <v>0.4253383847655812</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2666</v>
+        <v>2676</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2387635641666463</v>
+        <v>-0.2144791261187819</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2057045152274739</v>
+        <v>-0.1724524649345511</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.712583523300907</v>
+        <v>-0.6954691844987479</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.8065736263493122</v>
+        <v>-0.8070681187273152</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.250078104776442</v>
+        <v>-1.221578844133646</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.194422526968921</v>
+        <v>-1.210377779724283</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.146920712138098</v>
+        <v>-1.158926245631356</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.6208997775059188</v>
+        <v>-0.6531596039220275</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4368319740459938</v>
+        <v>-0.4659169664220499</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.007171886206066347</v>
+        <v>-0.01919248296199783</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4229530867807725</v>
+        <v>0.3745743938666379</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8159099115833115</v>
+        <v>0.7690640011866918</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9420831965382348</v>
+        <v>0.8970749834419962</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9643652837114516</v>
+        <v>0.9219045988205892</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2461</v>
+        <v>2470</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2541953827610683</v>
+        <v>-0.2254373404551231</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.04351912764676058</v>
+        <v>-0.007528392243486337</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6407196621993734</v>
+        <v>-0.6221948465566456</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4700086886515038</v>
+        <v>-0.4705031810295068</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6219529036847717</v>
+        <v>-0.5953798523457934</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9914050551622537</v>
+        <v>-1.010853442838602</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6709290286909919</v>
+        <v>-0.6666512324689293</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1027275690246299</v>
+        <v>-0.1203382438644169</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.3285191065129638</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8971598069846181</v>
+        <v>0.8812087443214551</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.162003049556859</v>
+        <v>1.122412426340027</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.585105094746908</v>
+        <v>1.544951633340538</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.472759144741694</v>
+        <v>1.433194516493323</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.478309291858956</v>
+        <v>1.439324398751594</v>
       </c>
     </row>
     <row r="20">
@@ -2942,205 +2942,205 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2262</v>
+        <v>2268</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.01178022806521994</v>
+        <v>0.02181243755246953</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2288855307228062</v>
+        <v>0.2679445701333734</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6068029616160047</v>
+        <v>-0.5866302478507066</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6088529503027758</v>
+        <v>-0.6093474426807788</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7944088173314512</v>
+        <v>-0.7458628975656794</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.290685581347162</v>
+        <v>-1.266728172397549</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7581119899960456</v>
+        <v>-0.7101003110057249</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.319170857753889</v>
+        <v>-0.2940988562215097</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.09117235583293137</v>
+        <v>-0.06652120080805446</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4960475465974667</v>
+        <v>0.5205849626450387</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8021928067960715</v>
+        <v>0.8014533334511071</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.480436243203187</v>
+        <v>1.476904021433292</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.572093967738255</v>
+        <v>1.566754913211611</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.488368963676542</v>
+        <v>1.507157799918332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 53.41</t>
+          <t>X &gt; 53.4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2795256401329524</v>
+        <v>0.3182678491302724</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.684662158686983</v>
+        <v>0.7268549748492461</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1901860383580214</v>
+        <v>-0.1684088561310588</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5880453882886272</v>
+        <v>-0.5885398806666302</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7902811727813344</v>
+        <v>-0.7417352530155625</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.117006999123205</v>
+        <v>-1.093049590173592</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.6256251836414179</v>
+        <v>-0.5776135046510973</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1541459652457107</v>
+        <v>-0.1313003216835043</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1957297335539678</v>
+        <v>0.2157885190116744</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8147561558689915</v>
+        <v>0.8321903750665882</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9260121885659913</v>
+        <v>0.9160960149044826</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.854129973833231</v>
+        <v>1.838401014391309</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.847115710227982</v>
+        <v>1.827304537659458</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.832119535707285</v>
+        <v>1.836310993529843</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 56.55</t>
+          <t>X &gt; 56.54</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1893</v>
+        <v>1899</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5469933954793333</v>
+        <v>0.5918860720635948</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.094838371399192</v>
+        <v>1.140798412419031</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1424817232031401</v>
+        <v>-0.1186058457259662</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6441681120002443</v>
+        <v>-0.6446626043782473</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7611833101722993</v>
+        <v>-0.7126373904065275</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.8850836354608518</v>
+        <v>-0.8611262265112387</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.7064975228997383</v>
+        <v>-0.6584858439094177</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.2247350855393293</v>
+        <v>0.2448230492090744</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.3510877091835596</v>
+        <v>0.3658283231686497</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.007266704392194</v>
+        <v>1.016459984586412</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.149303018716985</v>
+        <v>1.128275303243058</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.058767891252401</v>
+        <v>2.028990750455236</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.197671097495935</v>
+        <v>2.160425767545973</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.212101940538098</v>
+        <v>2.198833452099514</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 59.69</t>
+          <t>X &gt; 59.68</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.49932801362602</v>
+        <v>1.518873682359391</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.863737504525005</v>
+        <v>1.881189048193818</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1906395654410815</v>
+        <v>0.1850566768020627</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1439813107265024</v>
+        <v>-0.1759581881533165</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3336363490052392</v>
+        <v>-0.3167752733561073</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0799491855688359</v>
+        <v>0.07215426404586367</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.6925078559366113</v>
+        <v>0.7083622863186605</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.536703620349535</v>
+        <v>1.520113730348797</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.799564422821305</v>
+        <v>1.7735011676696</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.438009939338137</v>
+        <v>2.401472819142654</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.675066645832445</v>
+        <v>2.603836436647214</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.26826764879862</v>
+        <v>3.184651257635807</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.057737107146338</v>
+        <v>2.963709358946545</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.050236605769371</v>
+        <v>2.980466183795826</v>
       </c>
     </row>
     <row r="24">
@@ -3150,49 +3150,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.747618507877526</v>
+        <v>1.771922946523183</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.492145778273994</v>
+        <v>1.512381193049947</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.06444992612063061</v>
+        <v>0.1229021796566414</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.001001732071813421</v>
+        <v>-0.03456221198157294</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.08538336653711553</v>
+        <v>-0.0076823206754284</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4702217799475505</v>
+        <v>0.4586515852402755</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.095646992017734</v>
+        <v>1.107672915369648</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.214998193992948</v>
+        <v>2.190227251760504</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.578944506174281</v>
+        <v>2.540351416817259</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.254115793643898</v>
+        <v>3.200393803744205</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.735054997608799</v>
+        <v>3.641414646530698</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.196894289860502</v>
+        <v>4.086678158089143</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.075141013436202</v>
+        <v>4.014100876686598</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.717597337674391</v>
+        <v>3.682500577411652</v>
       </c>
     </row>
     <row r="25">
@@ -3202,569 +3202,569 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.402465893663894</v>
+        <v>2.398979084203923</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.73880166648928</v>
+        <v>1.729127392722809</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6151673079733015</v>
+        <v>0.5748813317954031</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.5996198568094897</v>
+        <v>0.5590989491207949</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.3528754932181641</v>
+        <v>0.3611826559474665</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.650249522853251</v>
+        <v>0.7068013867110352</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.294402137348015</v>
+        <v>1.301644204987397</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.764588545628989</v>
+        <v>2.802308167109516</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.18383553614045</v>
+        <v>3.202334829640598</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.691399691296311</v>
+        <v>3.689504063829261</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.115171956673123</v>
+        <v>4.068029311850346</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.705790136065069</v>
+        <v>4.636028532827766</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.769487274688778</v>
+        <v>4.677869877931819</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.26315850324621</v>
+        <v>4.125749408556068</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 69.12</t>
+          <t>X &gt; 69.11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.163435433900794</v>
+        <v>2.210021842615106</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.389069424518979</v>
+        <v>1.341493698652819</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.2411599644501266</v>
+        <v>0.278859389267879</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4550671164066955</v>
+        <v>0.4087434304825592</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6699156386248077</v>
+        <v>0.6720026507346475</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6325616347870877</v>
+        <v>0.6103400090184579</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.054127426148533</v>
+        <v>2.054700642201027</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.309618582758482</v>
+        <v>3.344720724627052</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.968216444235736</v>
+        <v>3.976644436560484</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.510225954526717</v>
+        <v>4.4069964577522</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.028086063939618</v>
+        <v>4.955364371420117</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.122374326434709</v>
+        <v>6.016875590390356</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.922873549804628</v>
+        <v>5.788941744094089</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.307566306843604</v>
+        <v>5.201866204771669</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 72.26</t>
+          <t>X &gt; 72.25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.350315783238685</v>
+        <v>1.26895794255487</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.19402784730385</v>
+        <v>1.139269229492044</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2172971996972137</v>
+        <v>0.164135892340127</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.7354951851866431</v>
+        <v>0.7785160575858185</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5851784739920234</v>
+        <v>0.6768638158587095</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4945796617260356</v>
+        <v>0.5620524354528271</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.155747091014675</v>
+        <v>2.148683167932795</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.143576604356937</v>
+        <v>3.136338779642479</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.304238058994969</v>
+        <v>4.262156868180092</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.6783373026134</v>
+        <v>4.601118985039534</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.736998632205498</v>
+        <v>5.656668459984061</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.999005134399916</v>
+        <v>6.877625895023378</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.67613054567795</v>
+        <v>6.579367193265753</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.318208608355846</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 75.4</t>
+          <t>X &gt; 75.39</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.554958408927533</v>
+        <v>1.525762614574901</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.176956172365941</v>
+        <v>1.175769385921285</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4458619176557548</v>
+        <v>0.4457085276514334</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.136625177836038</v>
+        <v>1.136130685458035</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.158873741332265</v>
+        <v>1.207419661098037</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.8957096543754304</v>
+        <v>0.9196670633250434</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.044183151611506</v>
+        <v>2.092194830601827</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.146621234282165</v>
+        <v>3.195868796675882</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.497867993725222</v>
+        <v>4.504187667359709</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.106983989763492</v>
+        <v>5.137758189683751</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.473551069438209</v>
+        <v>6.503124468605051</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.191430905295213</v>
+        <v>8.242905555745729</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.771280051981805</v>
+        <v>7.847747629181903</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.435848474374438</v>
+        <v>7.536254374605342</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 78.54</t>
+          <t>X &gt; 78.53</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.425333969465647</v>
+        <v>1.396138175113016</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.116231209735155</v>
+        <v>1.115044423290499</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2006264916467799</v>
+        <v>0.2004731016424586</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.502726635235142</v>
+        <v>1.502232142857139</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.136312082139447</v>
+        <v>2.184858001905219</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.78264444510787</v>
+        <v>1.806601854057483</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.60939241917503</v>
+        <v>2.657404098165351</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.965240442054963</v>
+        <v>4.01448800444868</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.154733622342263</v>
+        <v>5.149390395311883</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.869351983769896</v>
+        <v>5.888061814496901</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.881078465666164</v>
+        <v>7.897463033627474</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.479993775778986</v>
+        <v>9.518129770992367</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.668708633026199</v>
+        <v>8.732346844428541</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.372931897333565</v>
+        <v>8.460558373110565</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 81.68</t>
+          <t>X &gt; 81.67</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.614625370739532</v>
+        <v>2.727983413208257</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.118088959204371</v>
+        <v>1.938457121703195</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.723317574449332</v>
+        <v>1.54471913338849</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.445899405935783</v>
+        <v>3.261904761904752</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.38531685920951</v>
+        <v>3.248846097143321</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.727276876105741</v>
+        <v>2.727980822311444</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.075687535947857</v>
+        <v>4.095896161657421</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.882504242479591</v>
+        <v>4.741174512385186</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.512162990476362</v>
+        <v>6.450233649280136</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.895099058580314</v>
+        <v>7.848627290687368</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.647335699363182</v>
+        <v>8.596867795532233</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.75507908297848</v>
+        <v>10.87725675511934</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.65390749601276</v>
+        <v>10.79955914601585</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.40117424671775</v>
+        <v>10.57241353184073</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 84.82</t>
+          <t>X &gt; 84.81</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.082190765582148</v>
+        <v>1.947252516198283</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.218577488052304</v>
+        <v>2.302059927166468</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.017980860578817</v>
+        <v>2.102120388464165</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.701604062419605</v>
+        <v>3.782392026578073</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.328363053013227</v>
+        <v>4.45593358330057</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.237387568085211</v>
+        <v>4.147323753282294</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.929376237945263</v>
+        <v>4.861861462506432</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.209880409692502</v>
+        <v>6.140214748634719</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.508121554140601</v>
+        <v>7.459831286784748</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.599950330626271</v>
+        <v>8.573987202093804</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.366122958773843</v>
+        <v>9.338839002619721</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.53642344122627</v>
+        <v>11.52878868572105</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.69879685975751</v>
+        <v>11.71502610799443</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>11.7303577527025</v>
+        <v>11.77027252039739</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 87.97</t>
+          <t>X &gt; 87.95</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>385</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.324278774660449</v>
+        <v>2.295082980307818</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.271534240038179</v>
+        <v>2.270347453593523</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.175464153984443</v>
+        <v>3.175310763980121</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.825169817053322</v>
+        <v>3.824675324675319</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.806360783438144</v>
+        <v>3.854906703203916</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.103734813073231</v>
+        <v>4.127692222022844</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.577466012248621</v>
+        <v>5.625477691238942</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.889618147682661</v>
+        <v>5.938865710076378</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.38707754960145</v>
+        <v>7.460334659381147</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.13456135067419</v>
+        <v>9.233908675968763</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.449340711894507</v>
+        <v>9.549248747913182</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.60060198113296</v>
+        <v>12.72429860216121</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.69993164730006</v>
+        <v>12.84862119507789</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.92566729752659</v>
+        <v>13.09766605709326</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 91.11</t>
+          <t>X &gt; 91.1</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>268</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1310242679731104</v>
+        <v>0.1018284736204791</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.251181458491374</v>
+        <v>2.249994672046718</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.602678730452752</v>
+        <v>2.60252534044843</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.344844172548569</v>
+        <v>5.344349680170566</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.179688947811094</v>
+        <v>5.228234867576866</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.223331634162598</v>
+        <v>6.247289043112211</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.49683023012031</v>
+        <v>9.54484190911063</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.776030243049981</v>
+        <v>9.825277805443697</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>13.4463913701093</v>
+        <v>13.51964847988899</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.34274123049586</v>
+        <v>13.44208855579043</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>14.25744305731028</v>
+        <v>14.35735109332896</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.53062717981488</v>
+        <v>16.65432380084312</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.11047632650147</v>
+        <v>16.2591658742793</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>16.336211976728</v>
+        <v>16.50821073629466</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 94.25</t>
+          <t>X &gt; 94.24</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>165</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.246356696738367</v>
+        <v>0.2171609023857357</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.695776664280608</v>
+        <v>4.694589877835952</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.725247703767984</v>
+        <v>6.725094313763663</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.673654665538166</v>
+        <v>8.673160173160163</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.347486324563697</v>
+        <v>9.396032244329469</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9.644860354198784</v>
+        <v>9.668817763148397</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.77227120705382</v>
+        <v>10.82028288604414</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.72944498750952</v>
+        <v>12.77869254990323</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.30482646735037</v>
+        <v>16.37808357713006</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.8488470649599</v>
+        <v>14.94819439025447</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.0380853006391</v>
+        <v>14.13799333665777</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>17.70882708935806</v>
+        <v>17.8325237103863</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>17.89473684210526</v>
+        <v>18.04342638988309</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.332593704453</v>
+        <v>19.50459246401966</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 97.39</t>
+          <t>X &gt; 97.38</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.431707400211344</v>
+        <v>5.430520613766689</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.227412205932488</v>
+        <v>6.227258815928167</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13.500494492378</v>
+        <v>13.5</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.200300177377542</v>
+        <v>8.248846097143314</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>17.46970472776925</v>
+        <v>17.51895229016296</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15.02777019029408</v>
+        <v>15.10102730007377</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>14.17785139396422</v>
+        <v>14.27719871925879</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>12.78267404522785</v>
+        <v>12.88258208124653</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>14.00752838805935</v>
+        <v>14.13122500908759</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>15.96832991569833</v>
+        <v>16.11701946347616</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>19.76549413735344</v>
+        <v>19.9374928969201</v>
       </c>
     </row>
   </sheetData>
@@ -3904,261 +3904,261 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 6.277</t>
+          <t>X &lt; 6.285</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.852417302798983</v>
+        <v>5.823221508446352</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.058369906667124</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.374466632531153</v>
+        <v>4.42371419492487</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.273089489202327</v>
+        <v>2.372436814496901</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2781858976549216</v>
+        <v>-0.154489276626677</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.853553481694185</v>
+        <v>-2.681554722127522</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 9.419</t>
+          <t>X &lt; 9.426</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>128</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.894083969465647</v>
+        <v>6.864888175113016</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.189147876401819</v>
+        <v>9.187961089957163</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>11.13812649164678</v>
+        <v>11.13797310164246</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.580851635235142</v>
+        <v>6.580357142857139</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.948812082139447</v>
+        <v>9.997358001905219</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.214936111774534</v>
+        <v>3.238893520724147</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.692725752508366</v>
+        <v>4.740737431498687</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.569407108721627</v>
+        <v>6.618654671115344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.727174952198851</v>
+        <v>5.800432061978547</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.533506155868992</v>
+        <v>2.632853481163565</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.328804997608799</v>
+        <v>2.428713033627474</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.581933149964122</v>
+        <v>1.705629770992367</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3805322966507134</v>
+        <v>0.529221844428541</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.387517946877246</v>
+        <v>1.559516706443908</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 12.56</t>
+          <t>X &lt; 12.57</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>170</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.577907498877408</v>
+        <v>4.548711704524777</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.319662582284174</v>
+        <v>5.318475795839518</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.101361785764425</v>
+        <v>6.101208395760104</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.878645752882207</v>
+        <v>3.878151260504204</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.281532670374744</v>
+        <v>6.330078590140516</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.637730229421599</v>
+        <v>3.661687638371212</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.141255164273076</v>
+        <v>4.189266843263397</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.674186520486337</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.377910246316496</v>
+        <v>5.451167356096192</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.351520861751347</v>
+        <v>3.45086818704592</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.558584409373509</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.181197855846477</v>
+        <v>3.304894476874722</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.584576414297779</v>
+        <v>1.733265962075606</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.398547358641956</v>
+        <v>2.570546118208618</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 15.7</t>
+          <t>X &lt; 15.71</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>243</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.132252693745485</v>
+        <v>5.27677342101466</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.990202403150796</v>
+        <v>6.152612729301417</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.06456682086489</v>
+        <v>8.217891134429344</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.314133528239253</v>
+        <v>5.478922716627629</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.775843975143559</v>
+        <v>4.98967357567571</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.427127469799231</v>
+        <v>3.451084878748844</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.107849209298486</v>
+        <v>2.155860888288807</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.229257931766895</v>
+        <v>1.278505494160612</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.637411577713252</v>
+        <v>3.710668687492948</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.787492781383392</v>
+        <v>2.886840106677965</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.9367010881437707</v>
+        <v>1.036609124162446</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.794124507988819</v>
+        <v>1.917821129017064</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2721168803040186</v>
+        <v>-0.123427332526191</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.011231938646795</v>
+        <v>2.183230698213457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 18.84</t>
+          <t>X &lt; 18.85</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>340</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.342613381230358</v>
+        <v>6.210818407671162</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.084368464637116</v>
+        <v>6.953222717864136</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.748420609293838</v>
+        <v>8.885066124898273</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.231586929352787</v>
+        <v>6.689368770764112</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.61872428097498</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.225965523539244</v>
+        <v>4.610066990111903</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.670666928978953</v>
+        <v>2.968076612785239</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.497715932251033</v>
+        <v>2.671165668182795</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.848498481610612</v>
+        <v>1.921755591390308</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.880932626457231</v>
+        <v>1.980279951751804</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.499760879961741</v>
+        <v>0.5996689159804163</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.122374326434709</v>
+        <v>1.246070947462954</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4742471151139895</v>
+        <v>-0.3255575673361619</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.9279591233478328</v>
+        <v>1.099957882914495</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>438</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.509951549374328</v>
+        <v>5.408440211312119</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.181870479141544</v>
+        <v>6.087706565070285</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>8.070204117217557</v>
+        <v>8.182656359561008</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.232392731125557</v>
+        <v>5.597608274078858</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.780861168897445</v>
+        <v>4.203381757561331</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.849924696249417</v>
+        <v>4.156552250882882</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.167040821001521</v>
+        <v>2.411191976953234</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.928282679497883</v>
+        <v>2.075303304372746</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.867300522975107</v>
+        <v>1.940557632754803</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.474002731211456</v>
+        <v>1.57335005650603</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3560595638188389</v>
+        <v>0.4559675998375141</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.8470587207403781</v>
+        <v>0.9707553417686228</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4269078674269693</v>
+        <v>0.5755974152047969</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.109264522219711</v>
+        <v>1.281263281786373</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>563</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.469350399305796</v>
+        <v>3.299747330042592</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.811983133950662</v>
+        <v>3.653189963196603</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.371030576904332</v>
+        <v>5.548184369248098</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.369816999355926</v>
+        <v>3.565392354124739</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.653907552832173</v>
+        <v>2.900086875144659</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.352702541614683</v>
+        <v>1.687416448413742</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3305868585040628</v>
+        <v>-0.04062299252958468</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.9752753957188673</v>
+        <v>-0.7638121430439497</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.384701595182861</v>
+        <v>0.5366909272267719</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.82045698800313</v>
+        <v>-0.7211096627085567</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.090877506831696</v>
+        <v>-1.99096947081302</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.523639674192189</v>
+        <v>-1.399943053163945</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.654270101217847</v>
+        <v>-2.505580553440019</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.540434983850993</v>
+        <v>-1.368436224284331</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>707</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.115972229720242</v>
+        <v>1.971680892199849</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.62642687215854</v>
+        <v>2.48934414317845</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.928968075805194</v>
+        <v>3.916334446180279</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.917750503693419</v>
+        <v>4.04621848739496</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.096575519197444</v>
+        <v>3.136801279216151</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.9894233819301235</v>
+        <v>1.246870379069172</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.9047130226639553</v>
+        <v>1.124164397790814</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.411011915323634</v>
+        <v>-0.1071276776891565</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6595476537547214</v>
+        <v>0.9192700901475632</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.4732565739754193</v>
+        <v>-0.2486257148872113</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.385171310736325</v>
+        <v>-1.221534141513764</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.7850222955804256</v>
+        <v>-0.6613256745521809</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.346615864593986</v>
+        <v>-1.197926316816158</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5551093515668839</v>
+        <v>-0.3831105920002216</v>
       </c>
     </row>
     <row r="14">
@@ -4324,101 +4324,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.182602269347591</v>
+        <v>2.056632905792178</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.054469980420727</v>
+        <v>1.878608045460673</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.432748241055755</v>
+        <v>3.358406356911779</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.631517315708514</v>
+        <v>3.605386416861819</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.566600543677914</v>
+        <v>3.467425332115987</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.970483449052637</v>
+        <v>2.050074646163779</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.595832261384103</v>
+        <v>2.642732736663014</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.063674860200912</v>
+        <v>1.186626175228156</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.357722289476953</v>
+        <v>1.4511673560962</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2711171026145465</v>
+        <v>0.3406346943555576</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.6436432272432739</v>
+        <v>-0.5046596078819618</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6092650748879507</v>
+        <v>-0.4988418937065688</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.6743863424025491</v>
+        <v>-0.5918626709378927</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.9220234732410972</v>
+        <v>-0.8156310476932092</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 34.55</t>
+          <t>X &lt; 34.56</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.992245003262859</v>
+        <v>1.882780573928414</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.027300861476448</v>
+        <v>1.879070418683717</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.086831670929655</v>
+        <v>1.978915845966256</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.071068484686791</v>
+        <v>2.997250035255959</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.931582520823397</v>
+        <v>2.804150943662371</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.434340398913122</v>
+        <v>1.454061504913867</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.84813452618733</v>
+        <v>1.844471358303835</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6831596012440571</v>
+        <v>0.7414888295311926</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.120681931261664</v>
+        <v>1.156291824119286</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1280404543005034</v>
+        <v>-0.107721915661827</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.4324425098687712</v>
+        <v>-0.3557023089743154</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.09896166558921493</v>
+        <v>-0.04325193874917943</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.017617005443007</v>
+        <v>-0.9796400958699678</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.8915822525245503</v>
+        <v>-0.8744972377792024</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9496157018841771</v>
+        <v>0.8573221052067908</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.787726202582078</v>
+        <v>1.661186793281978</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.612782849035099</v>
+        <v>1.523203280670586</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.565105719499975</v>
+        <v>2.505602240896351</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.972645917049164</v>
+        <v>2.868868018955517</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.58214376439706</v>
+        <v>2.593629015604691</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.755386973488584</v>
+        <v>2.752586278637878</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.772411192986461</v>
+        <v>1.822981594192264</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.453475468105985</v>
+        <v>1.492530008941763</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.08764953506074136</v>
+        <v>0.117870604451241</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4609897143430572</v>
+        <v>-0.3809752697144333</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9425186987031182</v>
+        <v>-0.875309337069389</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.878576688731918</v>
+        <v>-1.823916567588626</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.652841038505386</v>
+        <v>-1.613808035824135</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6511594411637631</v>
+        <v>0.5679662531910878</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.270435640752268</v>
+        <v>1.161966345212413</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.82453994591738</v>
+        <v>1.744204332873686</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.602504434024858</v>
+        <v>2.549764049764043</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.745001567767282</v>
+        <v>2.661115509412724</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.588517806176959</v>
+        <v>2.601449869334211</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.352521516502314</v>
+        <v>2.358218634506201</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.507238046694397</v>
+        <v>1.559046883304958</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.294969959763144</v>
+        <v>1.338835676436382</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2181222678205756</v>
+        <v>0.2561343779231748</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2891507512565568</v>
+        <v>-0.2072692438989208</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.6329874249224119</v>
+        <v>-0.5597004176868836</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.9774953130315893</v>
+        <v>-0.91290428850197</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6761166976008184</v>
+        <v>-0.6218419481290312</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4017877468016309</v>
+        <v>0.3573898231024728</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.483494693377942</v>
+        <v>0.4222021908141116</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.253007049045586</v>
+        <v>1.215016608564007</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.48664512793102</v>
+        <v>1.476739806008098</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.276376823175312</v>
+        <v>2.211655495308918</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.241745540725404</v>
+        <v>2.258076689040976</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.223436243876236</v>
+        <v>2.234958039160503</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.291560163170502</v>
+        <v>1.344055365100807</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.031374819396717</v>
+        <v>1.07986327890977</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2478570854838722</v>
+        <v>0.2932398147175022</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.4880525721123234</v>
+        <v>-0.4034475623990161</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.184086106343983</v>
+        <v>-1.10355677639</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.405033772406398</v>
+        <v>-1.329614362468014</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.44490237184786</v>
+        <v>-1.375743744783698</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3470723076580668</v>
+        <v>0.3047459812650786</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1669410502641284</v>
+        <v>0.1144882228648854</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.9130097374144341</v>
+        <v>0.8815163401798998</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7251273361697201</v>
+        <v>0.7212088549871396</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9461835774665559</v>
+        <v>0.9027369217658432</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.535613681868</v>
+        <v>1.556550406255816</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.133038435150091</v>
+        <v>1.121551384987065</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.315297669797026</v>
+        <v>0.3391135134655485</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2716926690752572</v>
+        <v>-0.2476616516419341</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.06316611181073</v>
+        <v>-1.039522028446214</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.443203330854082</v>
+        <v>-1.386482187817748</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.051724068037053</v>
+        <v>-1.996083056995971</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.887421385406562</v>
+        <v>-1.834583581475776</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.895467149557582</v>
+        <v>-1.845511022686274</v>
       </c>
     </row>
     <row r="20">
@@ -4636,205 +4636,205 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1910</v>
+        <v>1915</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.003086087915683322</v>
+        <v>-0.04257935735451923</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1776971131597662</v>
+        <v>-0.2231590399129715</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7089489459548801</v>
+        <v>0.6818042704736271</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7635188243678499</v>
+        <v>0.7597402597402549</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9858775552183872</v>
+        <v>0.9228387711359929</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.626285484159474</v>
+        <v>1.588640010583738</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.047710053921236</v>
+        <v>0.9848841536631028</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5283127863773061</v>
+        <v>0.4959483983407509</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3103447585829429</v>
+        <v>0.2795987286452188</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3825881664753297</v>
+        <v>-0.411131015970355</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7442751960071092</v>
+        <v>-0.7427220550065172</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.547155023766912</v>
+        <v>-1.542446650499549</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.653334134537147</v>
+        <v>-1.648165942627834</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.555872105478777</v>
+        <v>-1.579354050736249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 53.41</t>
+          <t>X &lt; 53.4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2925240229225565</v>
+        <v>-0.3300170381571235</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5937679969918079</v>
+        <v>-0.6335732702324108</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1797931583134442</v>
+        <v>0.1575228646756344</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6219128548635382</v>
+        <v>0.6191604603926848</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8247951612624291</v>
+        <v>0.7723846733134749</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.196427528083539</v>
+        <v>1.166431471388279</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7566570502182941</v>
+        <v>0.7050824718403987</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2895884064315553</v>
+        <v>0.2655267034040421</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.009943368411839515</v>
+        <v>-0.03017957697633022</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6213125464210805</v>
+        <v>-0.6377026024866268</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7305938573530355</v>
+        <v>-0.7204340182032425</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.650414178280158</v>
+        <v>-1.634938735192215</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.641175718616466</v>
+        <v>-1.623398931392494</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.627846014936601</v>
+        <v>-1.633935674508471</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 56.55</t>
+          <t>X &lt; 56.54</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2279</v>
+        <v>2284</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.468667561592973</v>
+        <v>-0.5048807873978873</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8317082505128397</v>
+        <v>-0.8674824584299401</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1103243900706019</v>
+        <v>0.09013090460671691</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5710783106622088</v>
+        <v>0.5687507784281962</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.670355684242864</v>
+        <v>0.6267872430739985</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8167280889775128</v>
+        <v>0.7928856673210021</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.7124625946136263</v>
+        <v>0.6690984092376695</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.06162359303275622</v>
+        <v>-0.07826126774929065</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1226057495555324</v>
+        <v>-0.1348835780389308</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6655070020257483</v>
+        <v>-0.672434980374895</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7824888620403243</v>
+        <v>-0.7649495155636075</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.537584393895528</v>
+        <v>-1.51369437598926</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.650717703349279</v>
+        <v>-1.622378264980647</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.664122026795411</v>
+        <v>-1.65578539513227</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 59.69</t>
+          <t>X &lt; 59.68</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2457</v>
+        <v>2461</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.060461485079813</v>
+        <v>-1.073446507201837</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.22973915161279</v>
+        <v>-1.240192997456838</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1408133946245442</v>
+        <v>-0.136561499733503</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1333963325126675</v>
+        <v>0.1552003237555653</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2676637081557089</v>
+        <v>0.2548225768040027</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.01813354975745796</v>
+        <v>0.02339635588008804</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3698251018447678</v>
+        <v>-0.3798055182582019</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.9589441931498115</v>
+        <v>-0.9452513888765566</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.101293314684796</v>
+        <v>-1.08191789746995</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.544377285953622</v>
+        <v>-1.518705849465242</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.708394961707718</v>
+        <v>-1.660166836502398</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.121535116919524</v>
+        <v>-2.067081353652377</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.972117215147499</v>
+        <v>-1.912263736400057</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.968327596468299</v>
+        <v>-1.925474150931137</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2629</v>
+        <v>2633</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.039337881824189</v>
+        <v>-1.05343380748252</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8093696757803457</v>
+        <v>-0.8204928449652726</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.04496006871768543</v>
+        <v>-0.07915705348429469</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.02998285437681147</v>
+        <v>0.05072698773038553</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.0822657295558642</v>
+        <v>0.03627264989916057</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2075980957511163</v>
+        <v>-0.2002630487571153</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.5377875554764202</v>
+        <v>-0.5433534775922269</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.194970267704228</v>
+        <v>-1.178155200047982</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.37002086529165</v>
+        <v>-1.346317369408865</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.763665897362941</v>
+        <v>-1.732606795666172</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.044412682999564</v>
+        <v>-1.992047588527313</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.314217040149948</v>
+        <v>-2.254877819140454</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.240071315516595</v>
+        <v>-2.211975004470467</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.031676613792214</v>
+        <v>-2.018270038713709</v>
       </c>
     </row>
     <row r="25">
@@ -4896,569 +4896,569 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2806</v>
+        <v>2810</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.183368927797055</v>
+        <v>-1.180795979442102</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7848475005540863</v>
+        <v>-0.7788614020669442</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3068663934474927</v>
+        <v>-0.2863888267517325</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2641216743733921</v>
+        <v>-0.2436676798378983</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1423569281845189</v>
+        <v>-0.1461436830894627</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.252834543496121</v>
+        <v>-0.2797810711850062</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5319358078763941</v>
+        <v>-0.53415607222869</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.24838101026662</v>
+        <v>-1.264868056157383</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.416238834762325</v>
+        <v>-1.424812165374917</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.660528845912268</v>
+        <v>-1.660967592041843</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.86523000417246</v>
+        <v>-1.845804829863461</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.15147885573591</v>
+        <v>-2.123939930287854</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.17975225981526</v>
+        <v>-2.144148397478254</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.934604291184051</v>
+        <v>-1.875759094267835</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 69.12</t>
+          <t>X &lt; 69.11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2983</v>
+        <v>2987</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.8755648599657917</v>
+        <v>-0.8929060896418974</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4955815481548882</v>
+        <v>-0.4754162858347613</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1026700277641979</v>
+        <v>-0.1174471785443316</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1551083580691781</v>
+        <v>-0.136255302921974</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2398809855095791</v>
+        <v>-0.2402504760654054</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1922037542221133</v>
+        <v>-0.1829553941339483</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7278506549983419</v>
+        <v>-0.7264469372387907</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.22843136312823</v>
+        <v>-1.241090985416555</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.456973841366832</v>
+        <v>-1.460597349786163</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.670163415176582</v>
+        <v>-1.631240885269072</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.874864573436774</v>
+        <v>-1.850655695469513</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.309655321885735</v>
+        <v>-2.276157616093613</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.227125210051696</v>
+        <v>-2.184759079266243</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.983144976354403</v>
+        <v>-1.951008067576844</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 72.26</t>
+          <t>X &lt; 72.25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3144</v>
+        <v>3151</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4517467217201485</v>
+        <v>-0.4241446946720657</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3337767192213974</v>
+        <v>-0.3152301051108068</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.07697503119586457</v>
+        <v>-0.0594494157515939</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.2151059972624765</v>
+        <v>-0.2287024901703845</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.164779187701825</v>
+        <v>-0.1944932639175647</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1040738914010788</v>
+        <v>-0.125996476110295</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.6162005499058623</v>
+        <v>-0.612729952921832</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9389838191461877</v>
+        <v>-0.9347484806109776</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.285952629625115</v>
+        <v>-1.271415213053139</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.405016643622595</v>
+        <v>-1.38086482311536</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.75127685235941</v>
+        <v>-1.72622910334146</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.161908235922716</v>
+        <v>-2.12653404124994</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.056123108754697</v>
+        <v>-2.028677901764354</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.940249228695272</v>
+        <v>-1.921025185019118</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 75.4</t>
+          <t>X &lt; 75.39</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3281</v>
+        <v>3291</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4311134189339896</v>
+        <v>-0.4217341009160336</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2646416132701077</v>
+        <v>-0.2634372600277004</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.126496723181539</v>
+        <v>-0.1260335609862508</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.283700036497379</v>
+        <v>-0.282619985285848</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2886746159450695</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1875882191257148</v>
+        <v>-0.1934912928557253</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4687056439017354</v>
+        <v>-0.4802298213818474</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7671152588985777</v>
+        <v>-0.7779843188755535</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.101986642445091</v>
+        <v>-1.101873763264166</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.265723296185804</v>
+        <v>-1.271973908821259</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.636443175351005</v>
+        <v>-1.641661131521289</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.103244279216511</v>
+        <v>-2.113551067149146</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.988926112855687</v>
+        <v>-2.006280889471824</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.898922924808211</v>
+        <v>-1.922992409326376</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 78.54</t>
+          <t>X &lt; 78.53</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3405</v>
+        <v>3415</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3299063729399663</v>
+        <v>-0.3222471807796339</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1986595006473664</v>
+        <v>-0.1977534562932064</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.05056311303842875</v>
+        <v>-0.05036606940248589</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3144691029019384</v>
+        <v>-0.3133472367049137</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4560278680510024</v>
+        <v>-0.4655508765994512</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3478569714611055</v>
+        <v>-0.3521633007774554</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5046137373772979</v>
+        <v>-0.5138651400968683</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.8091669381991906</v>
+        <v>-0.8177217539065822</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.046102173900856</v>
+        <v>-1.043500686559462</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.205447716234268</v>
+        <v>-1.20804480780982</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.658137490654113</v>
+        <v>-1.659478160053041</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.018650207828649</v>
+        <v>-2.024341695206054</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.835685407400959</v>
+        <v>-1.847461410840779</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.770062816705725</v>
+        <v>-1.787390321374538</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 81.68</t>
+          <t>X &lt; 81.67</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3545</v>
+        <v>3553</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4707951421452634</v>
+        <v>-0.4910428400299978</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3238231584688265</v>
+        <v>-0.29244739531633</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.309658318479805</v>
+        <v>-0.2782726896033338</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5862488149618201</v>
+        <v>-0.5541678360931783</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5746452074749655</v>
+        <v>-0.5510523012952291</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4308972215588014</v>
+        <v>-0.4315115621177483</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6411590686687703</v>
+        <v>-0.6454985235574995</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.7831457081797737</v>
+        <v>-0.7589882763418103</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.041310963294109</v>
+        <v>-1.033639045385144</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.284250606599315</v>
+        <v>-1.279985638881421</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.417143424037192</v>
+        <v>-1.41250603273923</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.790194704560832</v>
+        <v>-1.817137458262209</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.771981098724353</v>
+        <v>-1.803097373354234</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.728226058764506</v>
+        <v>-1.763819206868789</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 84.82</t>
+          <t>X &lt; 84.81</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3657</v>
+        <v>3667</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3010795182727719</v>
+        <v>-0.2818509553217723</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2627208207908822</v>
+        <v>-0.2743163631550942</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2884002259104719</v>
+        <v>-0.2999687145619987</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4979082502298198</v>
+        <v>-0.5088970045456378</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.5850633952200752</v>
+        <v>-0.6026487989652907</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5457221419771656</v>
+        <v>-0.5327901527452354</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6156803610287582</v>
+        <v>-0.6059555461823152</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.7949885369240235</v>
+        <v>-0.7848217105889859</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9503578167798494</v>
+        <v>-0.9431681558863758</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.102582003103969</v>
+        <v>-1.098461215104486</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.210300193648031</v>
+        <v>-1.205908900977434</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.516164007729238</v>
+        <v>-1.514338203932688</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.538634597827141</v>
+        <v>-1.540196094502754</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.543932012105522</v>
+        <v>-1.54886548608404</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 87.97</t>
+          <t>X &lt; 87.95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3787</v>
+        <v>3798</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.244073925271195</v>
+        <v>-0.240366351258011</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1831787227032109</v>
+        <v>-0.1825277551871878</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3267892534822323</v>
+        <v>-0.3258297337474119</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3666562657393158</v>
+        <v>-0.3655462184874025</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3638525648573889</v>
+        <v>-0.3677999308502322</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3683148763677622</v>
+        <v>-0.3697178823236769</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4914466249296936</v>
+        <v>-0.4949721611425701</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5223985200682435</v>
+        <v>-0.525962836771086</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6480887608813219</v>
+        <v>-0.6537652822234037</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8241583785546425</v>
+        <v>-0.8320169817506979</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.8559740261379005</v>
+        <v>-0.8638004496663925</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.176462864815505</v>
+        <v>-1.185817597428688</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.186092571353512</v>
+        <v>-1.198000779946291</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.209772124419295</v>
+        <v>-1.224020681655091</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 91.11</t>
+          <t>X &lt; 91.1</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3904</v>
+        <v>3915</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.01729591309753431</v>
+        <v>-0.01520347458148308</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1084453309526268</v>
+        <v>-0.1080584542241496</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1829143768078794</v>
+        <v>-0.182391136768139</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3454066682906571</v>
+        <v>-0.3444040036396743</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3332205654455223</v>
+        <v>-0.3356886341804071</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3797724771825202</v>
+        <v>-0.3803870043841897</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5784644801687051</v>
+        <v>-0.5802085144472571</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5969132237591879</v>
+        <v>-0.5986926254926672</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.823013714979453</v>
+        <v>-0.8258434482255339</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.8145938953080787</v>
+        <v>-0.8192787592038826</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.8771794533766126</v>
+        <v>-0.8817291562653296</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.033434233548427</v>
+        <v>-1.039216412311184</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.004110789136739</v>
+        <v>-1.011731934938162</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.020268938368652</v>
+        <v>-1.0294839321257</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 94.25</t>
+          <t>X &lt; 94.24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4007</v>
+        <v>4018</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01822946337017584</v>
+        <v>-0.0169339533910744</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1483350173528493</v>
+        <v>-0.147879480762434</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2808008353815907</v>
+        <v>-0.2800276429591833</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3362351210506418</v>
+        <v>-0.3352957866364079</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3630654079004003</v>
+        <v>-0.3641471508139205</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3509885457597122</v>
+        <v>-0.3510530763945852</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3723589510292484</v>
+        <v>-0.3733930032839154</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.45210890174436</v>
+        <v>-0.4529780326619885</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5742333229756298</v>
+        <v>-0.5757952559433974</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5129987680901209</v>
+        <v>-0.515844306006997</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4794088427901997</v>
+        <v>-0.4823709628908048</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6306666255409894</v>
+        <v>-0.6342334130872374</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6377436514530856</v>
+        <v>-0.6423615718441624</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.697505137724697</v>
+        <v>-0.7029584055521099</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 97.39</t>
+          <t>X &lt; 97.38</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4088</v>
+        <v>4099</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03029423097326855</v>
+        <v>-0.02956707780526813</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.06771187969573589</v>
+        <v>-0.06750442938119505</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1321528447767335</v>
+        <v>-0.131795754805232</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2570876034178582</v>
+        <v>-0.2563884156729159</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1475617889857617</v>
+        <v>-0.1482420467802683</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1542045132254657</v>
+        <v>-0.1543223302619694</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1767797419971302</v>
+        <v>-0.1773702158466648</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2885710300179909</v>
+        <v>-0.2888894823560335</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2139898413511077</v>
+        <v>-0.2150406475731117</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.195141204834826</v>
+        <v>-0.1968214518123048</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1661916413547786</v>
+        <v>-0.1679623686153349</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1914470456348951</v>
+        <v>-0.1936783245940745</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2310551941783459</v>
+        <v>-0.2337354726446321</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3095221705395801</v>
+        <v>-0.312510007388731</v>
       </c>
     </row>
   </sheetData>
